--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5399800</v>
+        <v>5415200</v>
       </c>
       <c r="E8" s="3">
-        <v>4308900</v>
+        <v>4321200</v>
       </c>
       <c r="F8" s="3">
-        <v>3639700</v>
+        <v>3650100</v>
       </c>
       <c r="G8" s="3">
-        <v>3760900</v>
+        <v>3771700</v>
       </c>
       <c r="H8" s="3">
-        <v>3586000</v>
+        <v>3596300</v>
       </c>
       <c r="I8" s="3">
-        <v>3384900</v>
+        <v>3394600</v>
       </c>
       <c r="J8" s="3">
-        <v>3226600</v>
+        <v>3235800</v>
       </c>
       <c r="K8" s="3">
         <v>3144800</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3286900</v>
+        <v>3296300</v>
       </c>
       <c r="E9" s="3">
-        <v>2747300</v>
+        <v>2755200</v>
       </c>
       <c r="F9" s="3">
-        <v>2350300</v>
+        <v>2357000</v>
       </c>
       <c r="G9" s="3">
-        <v>2399500</v>
+        <v>2406400</v>
       </c>
       <c r="H9" s="3">
-        <v>2328800</v>
+        <v>2335400</v>
       </c>
       <c r="I9" s="3">
-        <v>2271700</v>
+        <v>2278200</v>
       </c>
       <c r="J9" s="3">
-        <v>2182200</v>
+        <v>2188400</v>
       </c>
       <c r="K9" s="3">
         <v>2145400</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2112800</v>
+        <v>2118900</v>
       </c>
       <c r="E10" s="3">
-        <v>1561500</v>
+        <v>1566000</v>
       </c>
       <c r="F10" s="3">
-        <v>1289500</v>
+        <v>1293200</v>
       </c>
       <c r="G10" s="3">
-        <v>1361400</v>
+        <v>1365300</v>
       </c>
       <c r="H10" s="3">
-        <v>1257300</v>
+        <v>1260800</v>
       </c>
       <c r="I10" s="3">
-        <v>1113200</v>
+        <v>1116400</v>
       </c>
       <c r="J10" s="3">
-        <v>1044400</v>
+        <v>1047400</v>
       </c>
       <c r="K10" s="3">
         <v>999300</v>
@@ -957,13 +957,13 @@
         <v>21200</v>
       </c>
       <c r="F14" s="3">
-        <v>127500</v>
+        <v>127800</v>
       </c>
       <c r="G14" s="3">
         <v>1700</v>
       </c>
       <c r="H14" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="I14" s="3">
         <v>16900</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>133200</v>
+        <v>133600</v>
       </c>
       <c r="E15" s="3">
-        <v>113700</v>
+        <v>114100</v>
       </c>
       <c r="F15" s="3">
-        <v>213300</v>
+        <v>213900</v>
       </c>
       <c r="G15" s="3">
-        <v>84300</v>
+        <v>84600</v>
       </c>
       <c r="H15" s="3">
-        <v>65100</v>
+        <v>65300</v>
       </c>
       <c r="I15" s="3">
-        <v>95100</v>
+        <v>95400</v>
       </c>
       <c r="J15" s="3">
-        <v>69500</v>
+        <v>69700</v>
       </c>
       <c r="K15" s="3">
         <v>56600</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4618300</v>
+        <v>4631500</v>
       </c>
       <c r="E17" s="3">
-        <v>3862200</v>
+        <v>3873300</v>
       </c>
       <c r="F17" s="3">
-        <v>3436100</v>
+        <v>3445900</v>
       </c>
       <c r="G17" s="3">
-        <v>3369200</v>
+        <v>3378800</v>
       </c>
       <c r="H17" s="3">
-        <v>3328300</v>
+        <v>3337800</v>
       </c>
       <c r="I17" s="3">
-        <v>3191100</v>
+        <v>3200200</v>
       </c>
       <c r="J17" s="3">
-        <v>3019900</v>
+        <v>3028500</v>
       </c>
       <c r="K17" s="3">
         <v>2973000</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>781500</v>
+        <v>783700</v>
       </c>
       <c r="E18" s="3">
-        <v>446600</v>
+        <v>447900</v>
       </c>
       <c r="F18" s="3">
-        <v>203600</v>
+        <v>204200</v>
       </c>
       <c r="G18" s="3">
-        <v>391800</v>
+        <v>392900</v>
       </c>
       <c r="H18" s="3">
-        <v>257700</v>
+        <v>258400</v>
       </c>
       <c r="I18" s="3">
-        <v>193800</v>
+        <v>194300</v>
       </c>
       <c r="J18" s="3">
-        <v>206700</v>
+        <v>207300</v>
       </c>
       <c r="K18" s="3">
         <v>171700</v>
@@ -1152,7 +1152,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>16600</v>
+        <v>16700</v>
       </c>
       <c r="E20" s="3">
         <v>1600</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1097700</v>
+        <v>1102800</v>
       </c>
       <c r="E21" s="3">
-        <v>720700</v>
+        <v>724500</v>
       </c>
       <c r="F21" s="3">
-        <v>465400</v>
+        <v>468400</v>
       </c>
       <c r="G21" s="3">
-        <v>643600</v>
+        <v>647100</v>
       </c>
       <c r="H21" s="3">
-        <v>458200</v>
+        <v>460800</v>
       </c>
       <c r="I21" s="3">
-        <v>404800</v>
+        <v>407300</v>
       </c>
       <c r="J21" s="3">
-        <v>418500</v>
+        <v>421000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>51200</v>
+        <v>51400</v>
       </c>
       <c r="E22" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F22" s="3">
+        <v>39200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>42400</v>
+      </c>
+      <c r="H22" s="3">
+        <v>44100</v>
+      </c>
+      <c r="I22" s="3">
         <v>42100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="J22" s="3">
         <v>39100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>42300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>44000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>42000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>39000</v>
       </c>
       <c r="K22" s="3">
         <v>51900</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>746900</v>
+        <v>749000</v>
       </c>
       <c r="E23" s="3">
-        <v>406100</v>
+        <v>407200</v>
       </c>
       <c r="F23" s="3">
-        <v>161400</v>
+        <v>161900</v>
       </c>
       <c r="G23" s="3">
-        <v>342100</v>
+        <v>343000</v>
       </c>
       <c r="H23" s="3">
-        <v>211900</v>
+        <v>212600</v>
       </c>
       <c r="I23" s="3">
-        <v>157200</v>
+        <v>157600</v>
       </c>
       <c r="J23" s="3">
-        <v>172000</v>
+        <v>172500</v>
       </c>
       <c r="K23" s="3">
         <v>113200</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>130000</v>
+        <v>130400</v>
       </c>
       <c r="E24" s="3">
-        <v>67500</v>
+        <v>67700</v>
       </c>
       <c r="F24" s="3">
-        <v>53000</v>
+        <v>53100</v>
       </c>
       <c r="G24" s="3">
-        <v>57000</v>
+        <v>57100</v>
       </c>
       <c r="H24" s="3">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="I24" s="3">
         <v>4600</v>
       </c>
       <c r="J24" s="3">
-        <v>46900</v>
+        <v>47000</v>
       </c>
       <c r="K24" s="3">
         <v>39400</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>616900</v>
+        <v>618600</v>
       </c>
       <c r="E26" s="3">
-        <v>338600</v>
+        <v>339600</v>
       </c>
       <c r="F26" s="3">
-        <v>108400</v>
+        <v>108700</v>
       </c>
       <c r="G26" s="3">
-        <v>285100</v>
+        <v>285900</v>
       </c>
       <c r="H26" s="3">
-        <v>159400</v>
+        <v>159800</v>
       </c>
       <c r="I26" s="3">
-        <v>152600</v>
+        <v>153000</v>
       </c>
       <c r="J26" s="3">
-        <v>125100</v>
+        <v>125500</v>
       </c>
       <c r="K26" s="3">
         <v>73900</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>616200</v>
+        <v>617900</v>
       </c>
       <c r="E27" s="3">
-        <v>337100</v>
+        <v>338100</v>
       </c>
       <c r="F27" s="3">
-        <v>96100</v>
+        <v>96300</v>
       </c>
       <c r="G27" s="3">
-        <v>270300</v>
+        <v>271000</v>
       </c>
       <c r="H27" s="3">
-        <v>144800</v>
+        <v>145300</v>
       </c>
       <c r="I27" s="3">
-        <v>133600</v>
+        <v>134000</v>
       </c>
       <c r="J27" s="3">
-        <v>88900</v>
+        <v>89200</v>
       </c>
       <c r="K27" s="3">
         <v>38700</v>
@@ -1656,7 +1656,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-16600</v>
+        <v>-16700</v>
       </c>
       <c r="E32" s="3">
         <v>-1600</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>616200</v>
+        <v>617900</v>
       </c>
       <c r="E33" s="3">
-        <v>337100</v>
+        <v>338100</v>
       </c>
       <c r="F33" s="3">
-        <v>96100</v>
+        <v>96300</v>
       </c>
       <c r="G33" s="3">
-        <v>270300</v>
+        <v>271000</v>
       </c>
       <c r="H33" s="3">
-        <v>144800</v>
+        <v>145300</v>
       </c>
       <c r="I33" s="3">
-        <v>133600</v>
+        <v>134000</v>
       </c>
       <c r="J33" s="3">
-        <v>88900</v>
+        <v>89200</v>
       </c>
       <c r="K33" s="3">
         <v>38700</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>616200</v>
+        <v>617900</v>
       </c>
       <c r="E35" s="3">
-        <v>337100</v>
+        <v>338100</v>
       </c>
       <c r="F35" s="3">
-        <v>96100</v>
+        <v>96300</v>
       </c>
       <c r="G35" s="3">
-        <v>270300</v>
+        <v>271000</v>
       </c>
       <c r="H35" s="3">
-        <v>144800</v>
+        <v>145300</v>
       </c>
       <c r="I35" s="3">
-        <v>133600</v>
+        <v>134000</v>
       </c>
       <c r="J35" s="3">
-        <v>88900</v>
+        <v>89200</v>
       </c>
       <c r="K35" s="3">
         <v>38700</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>325500</v>
+        <v>326500</v>
       </c>
       <c r="E41" s="3">
-        <v>395300</v>
+        <v>396400</v>
       </c>
       <c r="F41" s="3">
-        <v>722800</v>
+        <v>724800</v>
       </c>
       <c r="G41" s="3">
-        <v>139700</v>
+        <v>140100</v>
       </c>
       <c r="H41" s="3">
-        <v>176900</v>
+        <v>177400</v>
       </c>
       <c r="I41" s="3">
-        <v>183600</v>
+        <v>184200</v>
       </c>
       <c r="J41" s="3">
-        <v>213800</v>
+        <v>214400</v>
       </c>
       <c r="K41" s="3">
         <v>163900</v>
@@ -1964,10 +1964,10 @@
         <v>6700</v>
       </c>
       <c r="I42" s="3">
-        <v>85700</v>
+        <v>86000</v>
       </c>
       <c r="J42" s="3">
-        <v>57200</v>
+        <v>57400</v>
       </c>
       <c r="K42" s="3">
         <v>61800</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>581000</v>
+        <v>582700</v>
       </c>
       <c r="E43" s="3">
-        <v>544900</v>
+        <v>546500</v>
       </c>
       <c r="F43" s="3">
-        <v>367700</v>
+        <v>368700</v>
       </c>
       <c r="G43" s="3">
-        <v>381600</v>
+        <v>382700</v>
       </c>
       <c r="H43" s="3">
-        <v>368400</v>
+        <v>369400</v>
       </c>
       <c r="I43" s="3">
-        <v>321900</v>
+        <v>322900</v>
       </c>
       <c r="J43" s="3">
-        <v>285300</v>
+        <v>286200</v>
       </c>
       <c r="K43" s="3">
         <v>277000</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1124300</v>
+        <v>1127500</v>
       </c>
       <c r="E44" s="3">
-        <v>958400</v>
+        <v>961100</v>
       </c>
       <c r="F44" s="3">
-        <v>791000</v>
+        <v>793300</v>
       </c>
       <c r="G44" s="3">
-        <v>897900</v>
+        <v>900500</v>
       </c>
       <c r="H44" s="3">
-        <v>826400</v>
+        <v>828800</v>
       </c>
       <c r="I44" s="3">
-        <v>804600</v>
+        <v>806900</v>
       </c>
       <c r="J44" s="3">
-        <v>779400</v>
+        <v>781600</v>
       </c>
       <c r="K44" s="3">
         <v>797000</v>
@@ -2075,13 +2075,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>43100</v>
+        <v>43200</v>
       </c>
       <c r="E45" s="3">
         <v>4900</v>
       </c>
       <c r="F45" s="3">
-        <v>12900</v>
+        <v>13000</v>
       </c>
       <c r="G45" s="3">
         <v>3300</v>
@@ -2090,7 +2090,7 @@
         <v>10400</v>
       </c>
       <c r="I45" s="3">
-        <v>24700</v>
+        <v>24800</v>
       </c>
       <c r="J45" s="3">
         <v>22100</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2080000</v>
+        <v>2085900</v>
       </c>
       <c r="E46" s="3">
-        <v>1910300</v>
+        <v>1915700</v>
       </c>
       <c r="F46" s="3">
-        <v>1901500</v>
+        <v>1906900</v>
       </c>
       <c r="G46" s="3">
-        <v>1429900</v>
+        <v>1434000</v>
       </c>
       <c r="H46" s="3">
-        <v>1388800</v>
+        <v>1392700</v>
       </c>
       <c r="I46" s="3">
-        <v>1420600</v>
+        <v>1424700</v>
       </c>
       <c r="J46" s="3">
-        <v>1357800</v>
+        <v>1361700</v>
       </c>
       <c r="K46" s="3">
         <v>1314100</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>47500</v>
+        <v>47600</v>
       </c>
       <c r="E47" s="3">
-        <v>43700</v>
+        <v>43800</v>
       </c>
       <c r="F47" s="3">
-        <v>67700</v>
+        <v>67900</v>
       </c>
       <c r="G47" s="3">
-        <v>56600</v>
+        <v>56700</v>
       </c>
       <c r="H47" s="3">
-        <v>57000</v>
+        <v>57100</v>
       </c>
       <c r="I47" s="3">
-        <v>30500</v>
+        <v>30600</v>
       </c>
       <c r="J47" s="3">
-        <v>29800</v>
+        <v>29900</v>
       </c>
       <c r="K47" s="3">
         <v>24500</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2502900</v>
+        <v>2510000</v>
       </c>
       <c r="E48" s="3">
-        <v>2343700</v>
+        <v>2350400</v>
       </c>
       <c r="F48" s="3">
-        <v>1959200</v>
+        <v>1964800</v>
       </c>
       <c r="G48" s="3">
-        <v>2105400</v>
+        <v>2111400</v>
       </c>
       <c r="H48" s="3">
-        <v>1781900</v>
+        <v>1787000</v>
       </c>
       <c r="I48" s="3">
-        <v>1722400</v>
+        <v>1727300</v>
       </c>
       <c r="J48" s="3">
-        <v>1790700</v>
+        <v>1795900</v>
       </c>
       <c r="K48" s="3">
         <v>1805500</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>918700</v>
+        <v>921400</v>
       </c>
       <c r="E49" s="3">
-        <v>930200</v>
+        <v>932900</v>
       </c>
       <c r="F49" s="3">
-        <v>700400</v>
+        <v>702400</v>
       </c>
       <c r="G49" s="3">
-        <v>825000</v>
+        <v>827400</v>
       </c>
       <c r="H49" s="3">
-        <v>773300</v>
+        <v>775500</v>
       </c>
       <c r="I49" s="3">
-        <v>749600</v>
+        <v>751800</v>
       </c>
       <c r="J49" s="3">
-        <v>749100</v>
+        <v>751300</v>
       </c>
       <c r="K49" s="3">
         <v>742100</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>92100</v>
+        <v>92400</v>
       </c>
       <c r="E52" s="3">
-        <v>92700</v>
+        <v>93000</v>
       </c>
       <c r="F52" s="3">
-        <v>66100</v>
+        <v>66300</v>
       </c>
       <c r="G52" s="3">
-        <v>66900</v>
+        <v>67100</v>
       </c>
       <c r="H52" s="3">
-        <v>60100</v>
+        <v>60300</v>
       </c>
       <c r="I52" s="3">
-        <v>47800</v>
+        <v>47900</v>
       </c>
       <c r="J52" s="3">
-        <v>18800</v>
+        <v>18900</v>
       </c>
       <c r="K52" s="3">
         <v>19600</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5641200</v>
+        <v>5657300</v>
       </c>
       <c r="E54" s="3">
-        <v>5320600</v>
+        <v>5335800</v>
       </c>
       <c r="F54" s="3">
-        <v>4694800</v>
+        <v>4708200</v>
       </c>
       <c r="G54" s="3">
-        <v>4483900</v>
+        <v>4496700</v>
       </c>
       <c r="H54" s="3">
-        <v>4061100</v>
+        <v>4072700</v>
       </c>
       <c r="I54" s="3">
-        <v>3971000</v>
+        <v>3982300</v>
       </c>
       <c r="J54" s="3">
-        <v>3946300</v>
+        <v>3957600</v>
       </c>
       <c r="K54" s="3">
         <v>3905800</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>476900</v>
+        <v>478300</v>
       </c>
       <c r="E57" s="3">
-        <v>459000</v>
+        <v>460400</v>
       </c>
       <c r="F57" s="3">
-        <v>325400</v>
+        <v>326300</v>
       </c>
       <c r="G57" s="3">
-        <v>365000</v>
+        <v>366100</v>
       </c>
       <c r="H57" s="3">
-        <v>354700</v>
+        <v>355700</v>
       </c>
       <c r="I57" s="3">
-        <v>348900</v>
+        <v>349900</v>
       </c>
       <c r="J57" s="3">
-        <v>328400</v>
+        <v>329400</v>
       </c>
       <c r="K57" s="3">
         <v>292300</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>224700</v>
+        <v>225400</v>
       </c>
       <c r="E58" s="3">
-        <v>231100</v>
+        <v>231800</v>
       </c>
       <c r="F58" s="3">
-        <v>474900</v>
+        <v>476300</v>
       </c>
       <c r="G58" s="3">
-        <v>499300</v>
+        <v>500800</v>
       </c>
       <c r="H58" s="3">
-        <v>137700</v>
+        <v>138100</v>
       </c>
       <c r="I58" s="3">
-        <v>348000</v>
+        <v>349000</v>
       </c>
       <c r="J58" s="3">
-        <v>433900</v>
+        <v>435200</v>
       </c>
       <c r="K58" s="3">
         <v>253800</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>595700</v>
+        <v>597400</v>
       </c>
       <c r="E59" s="3">
-        <v>495700</v>
+        <v>497100</v>
       </c>
       <c r="F59" s="3">
-        <v>410600</v>
+        <v>411800</v>
       </c>
       <c r="G59" s="3">
-        <v>392000</v>
+        <v>393200</v>
       </c>
       <c r="H59" s="3">
-        <v>370600</v>
+        <v>371700</v>
       </c>
       <c r="I59" s="3">
-        <v>329100</v>
+        <v>330000</v>
       </c>
       <c r="J59" s="3">
-        <v>300200</v>
+        <v>301100</v>
       </c>
       <c r="K59" s="3">
         <v>309600</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1297300</v>
+        <v>1301000</v>
       </c>
       <c r="E60" s="3">
-        <v>1185800</v>
+        <v>1189200</v>
       </c>
       <c r="F60" s="3">
-        <v>1210900</v>
+        <v>1214400</v>
       </c>
       <c r="G60" s="3">
-        <v>1256400</v>
+        <v>1260000</v>
       </c>
       <c r="H60" s="3">
-        <v>863000</v>
+        <v>865400</v>
       </c>
       <c r="I60" s="3">
-        <v>1026000</v>
+        <v>1028900</v>
       </c>
       <c r="J60" s="3">
-        <v>1062600</v>
+        <v>1065600</v>
       </c>
       <c r="K60" s="3">
         <v>855800</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1350900</v>
+        <v>1354800</v>
       </c>
       <c r="E61" s="3">
-        <v>1438800</v>
+        <v>1442900</v>
       </c>
       <c r="F61" s="3">
-        <v>1258400</v>
+        <v>1262000</v>
       </c>
       <c r="G61" s="3">
-        <v>625200</v>
+        <v>627000</v>
       </c>
       <c r="H61" s="3">
-        <v>771000</v>
+        <v>773200</v>
       </c>
       <c r="I61" s="3">
-        <v>535900</v>
+        <v>537500</v>
       </c>
       <c r="J61" s="3">
-        <v>522400</v>
+        <v>523800</v>
       </c>
       <c r="K61" s="3">
         <v>537000</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>318200</v>
+        <v>319200</v>
       </c>
       <c r="E62" s="3">
-        <v>364200</v>
+        <v>365300</v>
       </c>
       <c r="F62" s="3">
-        <v>327900</v>
+        <v>328800</v>
       </c>
       <c r="G62" s="3">
-        <v>348900</v>
+        <v>349900</v>
       </c>
       <c r="H62" s="3">
-        <v>323200</v>
+        <v>324100</v>
       </c>
       <c r="I62" s="3">
-        <v>335400</v>
+        <v>336300</v>
       </c>
       <c r="J62" s="3">
-        <v>355300</v>
+        <v>356300</v>
       </c>
       <c r="K62" s="3">
         <v>339700</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2984200</v>
+        <v>2992700</v>
       </c>
       <c r="E66" s="3">
-        <v>2989800</v>
+        <v>2998400</v>
       </c>
       <c r="F66" s="3">
-        <v>2797900</v>
+        <v>2805900</v>
       </c>
       <c r="G66" s="3">
-        <v>2231400</v>
+        <v>2237800</v>
       </c>
       <c r="H66" s="3">
-        <v>1957800</v>
+        <v>1963400</v>
       </c>
       <c r="I66" s="3">
-        <v>1922700</v>
+        <v>1928200</v>
       </c>
       <c r="J66" s="3">
-        <v>1961700</v>
+        <v>1967300</v>
       </c>
       <c r="K66" s="3">
         <v>1751500</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1820500</v>
+        <v>1825700</v>
       </c>
       <c r="E72" s="3">
-        <v>1290800</v>
+        <v>1294500</v>
       </c>
       <c r="F72" s="3">
-        <v>1026600</v>
+        <v>1029500</v>
       </c>
       <c r="G72" s="3">
-        <v>1024100</v>
+        <v>1027000</v>
       </c>
       <c r="H72" s="3">
-        <v>825000</v>
+        <v>827400</v>
       </c>
       <c r="I72" s="3">
-        <v>731200</v>
+        <v>733300</v>
       </c>
       <c r="J72" s="3">
-        <v>636600</v>
+        <v>638400</v>
       </c>
       <c r="K72" s="3">
         <v>578700</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2657000</v>
+        <v>2664600</v>
       </c>
       <c r="E76" s="3">
-        <v>2330800</v>
+        <v>2337400</v>
       </c>
       <c r="F76" s="3">
-        <v>1896900</v>
+        <v>1902300</v>
       </c>
       <c r="G76" s="3">
-        <v>2252500</v>
+        <v>2258900</v>
       </c>
       <c r="H76" s="3">
-        <v>2103300</v>
+        <v>2109300</v>
       </c>
       <c r="I76" s="3">
-        <v>2048200</v>
+        <v>2054100</v>
       </c>
       <c r="J76" s="3">
-        <v>1984600</v>
+        <v>1990300</v>
       </c>
       <c r="K76" s="3">
         <v>2154200</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>616200</v>
+        <v>617900</v>
       </c>
       <c r="E81" s="3">
-        <v>337100</v>
+        <v>338100</v>
       </c>
       <c r="F81" s="3">
-        <v>96100</v>
+        <v>96300</v>
       </c>
       <c r="G81" s="3">
-        <v>270300</v>
+        <v>271000</v>
       </c>
       <c r="H81" s="3">
-        <v>144800</v>
+        <v>145300</v>
       </c>
       <c r="I81" s="3">
-        <v>133600</v>
+        <v>134000</v>
       </c>
       <c r="J81" s="3">
-        <v>88900</v>
+        <v>89200</v>
       </c>
       <c r="K81" s="3">
         <v>38700</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>299700</v>
+        <v>300600</v>
       </c>
       <c r="E83" s="3">
-        <v>272600</v>
+        <v>273400</v>
       </c>
       <c r="F83" s="3">
-        <v>265100</v>
+        <v>265800</v>
       </c>
       <c r="G83" s="3">
-        <v>259300</v>
+        <v>260000</v>
       </c>
       <c r="H83" s="3">
-        <v>202300</v>
+        <v>202900</v>
       </c>
       <c r="I83" s="3">
-        <v>205700</v>
+        <v>206300</v>
       </c>
       <c r="J83" s="3">
-        <v>207600</v>
+        <v>208200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>785300</v>
+        <v>787600</v>
       </c>
       <c r="E89" s="3">
-        <v>554000</v>
+        <v>555500</v>
       </c>
       <c r="F89" s="3">
-        <v>547600</v>
+        <v>549100</v>
       </c>
       <c r="G89" s="3">
-        <v>466300</v>
+        <v>467600</v>
       </c>
       <c r="H89" s="3">
-        <v>346600</v>
+        <v>347600</v>
       </c>
       <c r="I89" s="3">
-        <v>295500</v>
+        <v>296300</v>
       </c>
       <c r="J89" s="3">
-        <v>362100</v>
+        <v>363200</v>
       </c>
       <c r="K89" s="3">
         <v>228000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-382500</v>
+        <v>-383600</v>
       </c>
       <c r="E91" s="3">
-        <v>-303500</v>
+        <v>-304400</v>
       </c>
       <c r="F91" s="3">
-        <v>-218200</v>
+        <v>-218800</v>
       </c>
       <c r="G91" s="3">
-        <v>-277200</v>
+        <v>-278000</v>
       </c>
       <c r="H91" s="3">
-        <v>-234200</v>
+        <v>-234900</v>
       </c>
       <c r="I91" s="3">
-        <v>-177100</v>
+        <v>-177600</v>
       </c>
       <c r="J91" s="3">
-        <v>-177500</v>
+        <v>-178000</v>
       </c>
       <c r="K91" s="3">
         <v>-134900</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-361100</v>
+        <v>-362100</v>
       </c>
       <c r="E94" s="3">
-        <v>-723400</v>
+        <v>-725400</v>
       </c>
       <c r="F94" s="3">
-        <v>-160400</v>
+        <v>-160900</v>
       </c>
       <c r="G94" s="3">
-        <v>-286500</v>
+        <v>-287400</v>
       </c>
       <c r="H94" s="3">
-        <v>-229700</v>
+        <v>-230300</v>
       </c>
       <c r="I94" s="3">
-        <v>-193900</v>
+        <v>-194500</v>
       </c>
       <c r="J94" s="3">
-        <v>-142300</v>
+        <v>-142700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-91000</v>
+        <v>-91300</v>
       </c>
       <c r="E96" s="3">
-        <v>-73100</v>
+        <v>-73300</v>
       </c>
       <c r="F96" s="3">
-        <v>-73100</v>
+        <v>-73300</v>
       </c>
       <c r="G96" s="3">
-        <v>-62200</v>
+        <v>-62300</v>
       </c>
       <c r="H96" s="3">
-        <v>-37800</v>
+        <v>-37900</v>
       </c>
       <c r="I96" s="3">
-        <v>-34300</v>
+        <v>-34400</v>
       </c>
       <c r="J96" s="3">
-        <v>-25400</v>
+        <v>-25500</v>
       </c>
       <c r="K96" s="3">
         <v>-14600</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-486900</v>
+        <v>-488300</v>
       </c>
       <c r="E100" s="3">
-        <v>-160200</v>
+        <v>-160600</v>
       </c>
       <c r="F100" s="3">
-        <v>198800</v>
+        <v>199400</v>
       </c>
       <c r="G100" s="3">
-        <v>-218400</v>
+        <v>-219000</v>
       </c>
       <c r="H100" s="3">
-        <v>-123400</v>
+        <v>-123700</v>
       </c>
       <c r="I100" s="3">
-        <v>-130400</v>
+        <v>-130800</v>
       </c>
       <c r="J100" s="3">
-        <v>-172700</v>
+        <v>-173200</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-62800</v>
+        <v>-62900</v>
       </c>
       <c r="E102" s="3">
-        <v>-327500</v>
+        <v>-328400</v>
       </c>
       <c r="F102" s="3">
-        <v>583100</v>
+        <v>584700</v>
       </c>
       <c r="G102" s="3">
-        <v>-37200</v>
+        <v>-37300</v>
       </c>
       <c r="H102" s="3">
         <v>-6700</v>
       </c>
       <c r="I102" s="3">
-        <v>-30100</v>
+        <v>-30200</v>
       </c>
       <c r="J102" s="3">
-        <v>45700</v>
+        <v>45900</v>
       </c>
       <c r="K102" s="3">
         <v>-234300</v>

--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>WBRBY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5415200</v>
+        <v>4565200</v>
       </c>
       <c r="E8" s="3">
-        <v>4321200</v>
+        <v>5378400</v>
       </c>
       <c r="F8" s="3">
-        <v>3650100</v>
+        <v>4291800</v>
       </c>
       <c r="G8" s="3">
-        <v>3771700</v>
+        <v>3625300</v>
       </c>
       <c r="H8" s="3">
-        <v>3596300</v>
+        <v>3746000</v>
       </c>
       <c r="I8" s="3">
-        <v>3394600</v>
+        <v>3571800</v>
       </c>
       <c r="J8" s="3">
+        <v>3371500</v>
+      </c>
+      <c r="K8" s="3">
         <v>3235800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3144800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3092200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3132700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2586400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2248300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3296300</v>
+        <v>2822500</v>
       </c>
       <c r="E9" s="3">
-        <v>2755200</v>
+        <v>3273900</v>
       </c>
       <c r="F9" s="3">
-        <v>2357000</v>
+        <v>2736400</v>
       </c>
       <c r="G9" s="3">
-        <v>2406400</v>
+        <v>2340900</v>
       </c>
       <c r="H9" s="3">
-        <v>2335400</v>
+        <v>2390000</v>
       </c>
       <c r="I9" s="3">
-        <v>2278200</v>
+        <v>2319500</v>
       </c>
       <c r="J9" s="3">
+        <v>2262700</v>
+      </c>
+      <c r="K9" s="3">
         <v>2188400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2145400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2164100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2220300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1823800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1527600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2118900</v>
+        <v>1742700</v>
       </c>
       <c r="E10" s="3">
-        <v>1566000</v>
+        <v>2104400</v>
       </c>
       <c r="F10" s="3">
-        <v>1293200</v>
+        <v>1555300</v>
       </c>
       <c r="G10" s="3">
-        <v>1365300</v>
+        <v>1284400</v>
       </c>
       <c r="H10" s="3">
-        <v>1260800</v>
+        <v>1356000</v>
       </c>
       <c r="I10" s="3">
-        <v>1116400</v>
+        <v>1252300</v>
       </c>
       <c r="J10" s="3">
+        <v>1108800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1047400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>999300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>928100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>912400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>762600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>720700</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>21000</v>
+        <v>18500</v>
       </c>
       <c r="E14" s="3">
-        <v>21200</v>
+        <v>20400</v>
       </c>
       <c r="F14" s="3">
-        <v>127800</v>
+        <v>21100</v>
       </c>
       <c r="G14" s="3">
+        <v>127000</v>
+      </c>
+      <c r="H14" s="3">
         <v>1700</v>
       </c>
-      <c r="H14" s="3">
-        <v>11700</v>
-      </c>
       <c r="I14" s="3">
-        <v>16900</v>
+        <v>11600</v>
       </c>
       <c r="J14" s="3">
+        <v>16800</v>
+      </c>
+      <c r="K14" s="3">
         <v>7800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>291300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>57900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-36000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>133600</v>
+        <v>103800</v>
       </c>
       <c r="E15" s="3">
-        <v>114100</v>
+        <v>132700</v>
       </c>
       <c r="F15" s="3">
-        <v>213900</v>
+        <v>113300</v>
       </c>
       <c r="G15" s="3">
-        <v>84600</v>
+        <v>212400</v>
       </c>
       <c r="H15" s="3">
-        <v>65300</v>
+        <v>84000</v>
       </c>
       <c r="I15" s="3">
-        <v>95400</v>
+        <v>64900</v>
       </c>
       <c r="J15" s="3">
+        <v>94700</v>
+      </c>
+      <c r="K15" s="3">
         <v>69700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>56600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>59100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>68100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>58000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4631500</v>
+        <v>4049200</v>
       </c>
       <c r="E17" s="3">
-        <v>3873300</v>
+        <v>4599400</v>
       </c>
       <c r="F17" s="3">
-        <v>3445900</v>
+        <v>3846900</v>
       </c>
       <c r="G17" s="3">
-        <v>3378800</v>
+        <v>3422500</v>
       </c>
       <c r="H17" s="3">
-        <v>3337800</v>
+        <v>3355800</v>
       </c>
       <c r="I17" s="3">
-        <v>3200200</v>
+        <v>3315100</v>
       </c>
       <c r="J17" s="3">
+        <v>3178400</v>
+      </c>
+      <c r="K17" s="3">
         <v>3028500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2973000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3274100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3056600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2610200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2204300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>783700</v>
+        <v>516100</v>
       </c>
       <c r="E18" s="3">
-        <v>447900</v>
+        <v>778900</v>
       </c>
       <c r="F18" s="3">
-        <v>204200</v>
+        <v>444900</v>
       </c>
       <c r="G18" s="3">
-        <v>392900</v>
+        <v>202800</v>
       </c>
       <c r="H18" s="3">
-        <v>258400</v>
+        <v>390200</v>
       </c>
       <c r="I18" s="3">
-        <v>194300</v>
+        <v>256700</v>
       </c>
       <c r="J18" s="3">
+        <v>193000</v>
+      </c>
+      <c r="K18" s="3">
         <v>207300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>171700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-181900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>76100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>44000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,76 +1178,80 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>16700</v>
+        <v>21900</v>
       </c>
       <c r="E20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H20" s="3">
         <v>-7400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>51500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>71500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1102800</v>
+        <v>846000</v>
       </c>
       <c r="E21" s="3">
-        <v>724500</v>
+        <v>1091600</v>
       </c>
       <c r="F21" s="3">
-        <v>468400</v>
+        <v>716200</v>
       </c>
       <c r="G21" s="3">
-        <v>647100</v>
+        <v>462000</v>
       </c>
       <c r="H21" s="3">
-        <v>460800</v>
+        <v>639500</v>
       </c>
       <c r="I21" s="3">
-        <v>407300</v>
+        <v>455100</v>
       </c>
       <c r="J21" s="3">
+        <v>402000</v>
+      </c>
+      <c r="K21" s="3">
         <v>421000</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
@@ -1223,141 +1259,153 @@
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>241700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>331500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>51400</v>
+        <v>79400</v>
       </c>
       <c r="E22" s="3">
-        <v>42200</v>
+        <v>51000</v>
       </c>
       <c r="F22" s="3">
-        <v>39200</v>
+        <v>42000</v>
       </c>
       <c r="G22" s="3">
-        <v>42400</v>
+        <v>38900</v>
       </c>
       <c r="H22" s="3">
-        <v>44100</v>
+        <v>42100</v>
       </c>
       <c r="I22" s="3">
-        <v>42100</v>
+        <v>43800</v>
       </c>
       <c r="J22" s="3">
+        <v>41800</v>
+      </c>
+      <c r="K22" s="3">
         <v>39100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>66600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>75100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>67400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>59800</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>749000</v>
+        <v>458600</v>
       </c>
       <c r="E23" s="3">
-        <v>407200</v>
+        <v>743900</v>
       </c>
       <c r="F23" s="3">
-        <v>161900</v>
+        <v>404500</v>
       </c>
       <c r="G23" s="3">
-        <v>343000</v>
+        <v>160800</v>
       </c>
       <c r="H23" s="3">
-        <v>212600</v>
+        <v>340700</v>
       </c>
       <c r="I23" s="3">
-        <v>157600</v>
+        <v>211100</v>
       </c>
       <c r="J23" s="3">
+        <v>156600</v>
+      </c>
+      <c r="K23" s="3">
         <v>172500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>113200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-234900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>55700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>130400</v>
+        <v>96400</v>
       </c>
       <c r="E24" s="3">
-        <v>67700</v>
+        <v>129500</v>
       </c>
       <c r="F24" s="3">
-        <v>53100</v>
+        <v>67200</v>
       </c>
       <c r="G24" s="3">
-        <v>57100</v>
+        <v>52800</v>
       </c>
       <c r="H24" s="3">
-        <v>52700</v>
+        <v>56700</v>
       </c>
       <c r="I24" s="3">
+        <v>52400</v>
+      </c>
+      <c r="J24" s="3">
         <v>4600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>47000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>618600</v>
+        <v>362200</v>
       </c>
       <c r="E26" s="3">
-        <v>339600</v>
+        <v>614400</v>
       </c>
       <c r="F26" s="3">
-        <v>108700</v>
+        <v>337300</v>
       </c>
       <c r="G26" s="3">
-        <v>285900</v>
+        <v>108000</v>
       </c>
       <c r="H26" s="3">
-        <v>159800</v>
+        <v>284000</v>
       </c>
       <c r="I26" s="3">
-        <v>153000</v>
+        <v>158700</v>
       </c>
       <c r="J26" s="3">
+        <v>152000</v>
+      </c>
+      <c r="K26" s="3">
         <v>125500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>73900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-250500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-44500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46300</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>617900</v>
+        <v>361300</v>
       </c>
       <c r="E27" s="3">
-        <v>338100</v>
+        <v>613700</v>
       </c>
       <c r="F27" s="3">
-        <v>96300</v>
+        <v>335800</v>
       </c>
       <c r="G27" s="3">
-        <v>271000</v>
+        <v>95700</v>
       </c>
       <c r="H27" s="3">
-        <v>145300</v>
+        <v>269200</v>
       </c>
       <c r="I27" s="3">
-        <v>134000</v>
+        <v>144300</v>
       </c>
       <c r="J27" s="3">
+        <v>133100</v>
+      </c>
+      <c r="K27" s="3">
         <v>89200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>38700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-285500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-45800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-77200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-16700</v>
+        <v>-21900</v>
       </c>
       <c r="E32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
-        <v>3200</v>
-      </c>
       <c r="G32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H32" s="3">
         <v>7400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-51500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-71500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>617900</v>
+        <v>361300</v>
       </c>
       <c r="E33" s="3">
-        <v>338100</v>
+        <v>613700</v>
       </c>
       <c r="F33" s="3">
-        <v>96300</v>
+        <v>335800</v>
       </c>
       <c r="G33" s="3">
-        <v>271000</v>
+        <v>95700</v>
       </c>
       <c r="H33" s="3">
-        <v>145300</v>
+        <v>269200</v>
       </c>
       <c r="I33" s="3">
-        <v>134000</v>
+        <v>144300</v>
       </c>
       <c r="J33" s="3">
+        <v>133100</v>
+      </c>
+      <c r="K33" s="3">
         <v>89200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>38700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-285500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-45800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-77200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>617900</v>
+        <v>361300</v>
       </c>
       <c r="E35" s="3">
-        <v>338100</v>
+        <v>613700</v>
       </c>
       <c r="F35" s="3">
-        <v>96300</v>
+        <v>335800</v>
       </c>
       <c r="G35" s="3">
-        <v>271000</v>
+        <v>95700</v>
       </c>
       <c r="H35" s="3">
-        <v>145300</v>
+        <v>269200</v>
       </c>
       <c r="I35" s="3">
-        <v>134000</v>
+        <v>144300</v>
       </c>
       <c r="J35" s="3">
+        <v>133100</v>
+      </c>
+      <c r="K35" s="3">
         <v>89200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>38700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-285500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-45800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-77200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>326500</v>
+        <v>447500</v>
       </c>
       <c r="E41" s="3">
-        <v>396400</v>
+        <v>324200</v>
       </c>
       <c r="F41" s="3">
-        <v>724800</v>
+        <v>393700</v>
       </c>
       <c r="G41" s="3">
-        <v>140100</v>
+        <v>719900</v>
       </c>
       <c r="H41" s="3">
-        <v>177400</v>
+        <v>139100</v>
       </c>
       <c r="I41" s="3">
-        <v>184200</v>
+        <v>176200</v>
       </c>
       <c r="J41" s="3">
+        <v>182900</v>
+      </c>
+      <c r="K41" s="3">
         <v>214400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>163900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>169000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>584300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>266000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1167700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E42" s="3">
         <v>6000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7100</v>
       </c>
-      <c r="G42" s="3">
-        <v>7500</v>
-      </c>
       <c r="H42" s="3">
-        <v>6700</v>
+        <v>7400</v>
       </c>
       <c r="I42" s="3">
-        <v>86000</v>
+        <v>6600</v>
       </c>
       <c r="J42" s="3">
+        <v>85400</v>
+      </c>
+      <c r="K42" s="3">
         <v>57400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>61800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>63700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>107600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>79600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>100300</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>582700</v>
+        <v>490700</v>
       </c>
       <c r="E43" s="3">
-        <v>546500</v>
+        <v>563700</v>
       </c>
       <c r="F43" s="3">
-        <v>368700</v>
+        <v>542700</v>
       </c>
       <c r="G43" s="3">
-        <v>382700</v>
+        <v>366200</v>
       </c>
       <c r="H43" s="3">
-        <v>369400</v>
+        <v>380100</v>
       </c>
       <c r="I43" s="3">
-        <v>322900</v>
+        <v>366900</v>
       </c>
       <c r="J43" s="3">
+        <v>320700</v>
+      </c>
+      <c r="K43" s="3">
         <v>286200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>277000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>285600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>331300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>296800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>203800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1127500</v>
+        <v>1246900</v>
       </c>
       <c r="E44" s="3">
-        <v>961100</v>
+        <v>1119800</v>
       </c>
       <c r="F44" s="3">
-        <v>793300</v>
+        <v>954600</v>
       </c>
       <c r="G44" s="3">
-        <v>900500</v>
+        <v>787900</v>
       </c>
       <c r="H44" s="3">
-        <v>828800</v>
+        <v>894400</v>
       </c>
       <c r="I44" s="3">
-        <v>806900</v>
+        <v>823100</v>
       </c>
       <c r="J44" s="3">
+        <v>801400</v>
+      </c>
+      <c r="K44" s="3">
         <v>781600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>797000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>821800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>783500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>766600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>674800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>43200</v>
+        <v>50500</v>
       </c>
       <c r="E45" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
-        <v>13000</v>
-      </c>
       <c r="G45" s="3">
-        <v>3300</v>
+        <v>12900</v>
       </c>
       <c r="H45" s="3">
-        <v>10400</v>
+        <v>3200</v>
       </c>
       <c r="I45" s="3">
-        <v>24800</v>
+        <v>10300</v>
       </c>
       <c r="J45" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K45" s="3">
         <v>22100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2085900</v>
+        <v>2242200</v>
       </c>
       <c r="E46" s="3">
-        <v>1915700</v>
+        <v>2071700</v>
       </c>
       <c r="F46" s="3">
-        <v>1906900</v>
+        <v>1902700</v>
       </c>
       <c r="G46" s="3">
-        <v>1434000</v>
+        <v>1893900</v>
       </c>
       <c r="H46" s="3">
-        <v>1392700</v>
+        <v>1424300</v>
       </c>
       <c r="I46" s="3">
-        <v>1424700</v>
+        <v>1383300</v>
       </c>
       <c r="J46" s="3">
+        <v>1415000</v>
+      </c>
+      <c r="K46" s="3">
         <v>1361700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1314100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1355000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1822100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1426800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1570600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>47600</v>
+        <v>63500</v>
       </c>
       <c r="E47" s="3">
-        <v>43800</v>
+        <v>47300</v>
       </c>
       <c r="F47" s="3">
-        <v>67900</v>
+        <v>43500</v>
       </c>
       <c r="G47" s="3">
-        <v>56700</v>
+        <v>67400</v>
       </c>
       <c r="H47" s="3">
-        <v>57100</v>
+        <v>56300</v>
       </c>
       <c r="I47" s="3">
-        <v>30600</v>
+        <v>56800</v>
       </c>
       <c r="J47" s="3">
+        <v>30300</v>
+      </c>
+      <c r="K47" s="3">
         <v>29900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>25300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>36800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>37700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>161400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2510000</v>
+        <v>2604100</v>
       </c>
       <c r="E48" s="3">
-        <v>2350400</v>
+        <v>2493000</v>
       </c>
       <c r="F48" s="3">
-        <v>1964800</v>
+        <v>2334400</v>
       </c>
       <c r="G48" s="3">
-        <v>2111400</v>
+        <v>1951400</v>
       </c>
       <c r="H48" s="3">
-        <v>1787000</v>
+        <v>2097100</v>
       </c>
       <c r="I48" s="3">
-        <v>1727300</v>
+        <v>1774800</v>
       </c>
       <c r="J48" s="3">
+        <v>1715600</v>
+      </c>
+      <c r="K48" s="3">
         <v>1795900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1805500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1861600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2048900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2069000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4133600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>921400</v>
+        <v>923900</v>
       </c>
       <c r="E49" s="3">
-        <v>932900</v>
+        <v>915100</v>
       </c>
       <c r="F49" s="3">
-        <v>702400</v>
+        <v>926600</v>
       </c>
       <c r="G49" s="3">
-        <v>827400</v>
+        <v>697700</v>
       </c>
       <c r="H49" s="3">
-        <v>775500</v>
+        <v>821700</v>
       </c>
       <c r="I49" s="3">
-        <v>751800</v>
+        <v>770200</v>
       </c>
       <c r="J49" s="3">
+        <v>746700</v>
+      </c>
+      <c r="K49" s="3">
         <v>751300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>742100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>765200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>991600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>968500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1595300</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>91700</v>
+      </c>
+      <c r="F52" s="3">
         <v>92400</v>
       </c>
-      <c r="E52" s="3">
-        <v>93000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>66300</v>
-      </c>
       <c r="G52" s="3">
-        <v>67100</v>
+        <v>65800</v>
       </c>
       <c r="H52" s="3">
-        <v>60300</v>
+        <v>66700</v>
       </c>
       <c r="I52" s="3">
-        <v>47900</v>
+        <v>59900</v>
       </c>
       <c r="J52" s="3">
+        <v>47600</v>
+      </c>
+      <c r="K52" s="3">
         <v>18900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>49300</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5657300</v>
+        <v>5909900</v>
       </c>
       <c r="E54" s="3">
-        <v>5335800</v>
+        <v>5618800</v>
       </c>
       <c r="F54" s="3">
-        <v>4708200</v>
+        <v>5299500</v>
       </c>
       <c r="G54" s="3">
-        <v>4496700</v>
+        <v>4676200</v>
       </c>
       <c r="H54" s="3">
-        <v>4072700</v>
+        <v>4466100</v>
       </c>
       <c r="I54" s="3">
-        <v>3982300</v>
+        <v>4045000</v>
       </c>
       <c r="J54" s="3">
+        <v>3955200</v>
+      </c>
+      <c r="K54" s="3">
         <v>3957600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3905800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4027200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4954200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4545400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4685100</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>478300</v>
+        <v>356700</v>
       </c>
       <c r="E57" s="3">
-        <v>460400</v>
+        <v>475000</v>
       </c>
       <c r="F57" s="3">
-        <v>326300</v>
+        <v>457200</v>
       </c>
       <c r="G57" s="3">
-        <v>366100</v>
+        <v>324100</v>
       </c>
       <c r="H57" s="3">
-        <v>355700</v>
+        <v>363600</v>
       </c>
       <c r="I57" s="3">
-        <v>349900</v>
+        <v>353300</v>
       </c>
       <c r="J57" s="3">
+        <v>347500</v>
+      </c>
+      <c r="K57" s="3">
         <v>329400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>292300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>301400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>315700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>278000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>442200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>225400</v>
+        <v>461000</v>
       </c>
       <c r="E58" s="3">
-        <v>231800</v>
+        <v>223800</v>
       </c>
       <c r="F58" s="3">
-        <v>476300</v>
+        <v>230200</v>
       </c>
       <c r="G58" s="3">
-        <v>500800</v>
+        <v>473000</v>
       </c>
       <c r="H58" s="3">
-        <v>138100</v>
+        <v>497400</v>
       </c>
       <c r="I58" s="3">
-        <v>349000</v>
+        <v>137100</v>
       </c>
       <c r="J58" s="3">
+        <v>346600</v>
+      </c>
+      <c r="K58" s="3">
         <v>435200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>253800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>261700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>342200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>987600</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>597400</v>
+        <v>509300</v>
       </c>
       <c r="E59" s="3">
-        <v>497100</v>
+        <v>593300</v>
       </c>
       <c r="F59" s="3">
-        <v>411800</v>
+        <v>493700</v>
       </c>
       <c r="G59" s="3">
-        <v>393200</v>
+        <v>409000</v>
       </c>
       <c r="H59" s="3">
-        <v>371700</v>
+        <v>390500</v>
       </c>
       <c r="I59" s="3">
-        <v>330000</v>
+        <v>369100</v>
       </c>
       <c r="J59" s="3">
+        <v>327800</v>
+      </c>
+      <c r="K59" s="3">
         <v>301100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>309600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>319300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>332400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>335000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>231300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1301000</v>
+        <v>1327100</v>
       </c>
       <c r="E60" s="3">
-        <v>1189200</v>
+        <v>1292200</v>
       </c>
       <c r="F60" s="3">
-        <v>1214400</v>
+        <v>1181100</v>
       </c>
       <c r="G60" s="3">
-        <v>1260000</v>
+        <v>1206100</v>
       </c>
       <c r="H60" s="3">
-        <v>865400</v>
+        <v>1251400</v>
       </c>
       <c r="I60" s="3">
-        <v>1028900</v>
+        <v>859600</v>
       </c>
       <c r="J60" s="3">
+        <v>1021900</v>
+      </c>
+      <c r="K60" s="3">
         <v>1065600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>855800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>882400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>990300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>676700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>946200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1354800</v>
+        <v>1377400</v>
       </c>
       <c r="E61" s="3">
-        <v>1442900</v>
+        <v>1345500</v>
       </c>
       <c r="F61" s="3">
-        <v>1262000</v>
+        <v>1433100</v>
       </c>
       <c r="G61" s="3">
-        <v>627000</v>
+        <v>1253400</v>
       </c>
       <c r="H61" s="3">
-        <v>773200</v>
+        <v>622700</v>
       </c>
       <c r="I61" s="3">
-        <v>537500</v>
+        <v>767900</v>
       </c>
       <c r="J61" s="3">
+        <v>533800</v>
+      </c>
+      <c r="K61" s="3">
         <v>523800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>537000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>553700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>983600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>942900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>603200</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>319200</v>
+        <v>320800</v>
       </c>
       <c r="E62" s="3">
-        <v>365300</v>
+        <v>317000</v>
       </c>
       <c r="F62" s="3">
-        <v>328800</v>
+        <v>362800</v>
       </c>
       <c r="G62" s="3">
-        <v>349900</v>
+        <v>326600</v>
       </c>
       <c r="H62" s="3">
-        <v>324100</v>
+        <v>347500</v>
       </c>
       <c r="I62" s="3">
-        <v>336300</v>
+        <v>321900</v>
       </c>
       <c r="J62" s="3">
+        <v>334000</v>
+      </c>
+      <c r="K62" s="3">
         <v>356300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>339700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>350200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>328600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>330500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>387900</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2992700</v>
+        <v>3040200</v>
       </c>
       <c r="E66" s="3">
-        <v>2998400</v>
+        <v>2972400</v>
       </c>
       <c r="F66" s="3">
-        <v>2805900</v>
+        <v>2978000</v>
       </c>
       <c r="G66" s="3">
-        <v>2237800</v>
+        <v>2786800</v>
       </c>
       <c r="H66" s="3">
-        <v>1963400</v>
+        <v>2222600</v>
       </c>
       <c r="I66" s="3">
-        <v>1928200</v>
+        <v>1950000</v>
       </c>
       <c r="J66" s="3">
+        <v>1915100</v>
+      </c>
+      <c r="K66" s="3">
         <v>1967300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1751500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1806000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2304700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1953800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1835600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1825700</v>
+        <v>2076600</v>
       </c>
       <c r="E72" s="3">
-        <v>1294500</v>
+        <v>1813300</v>
       </c>
       <c r="F72" s="3">
-        <v>1029500</v>
+        <v>1285700</v>
       </c>
       <c r="G72" s="3">
-        <v>1027000</v>
+        <v>1022500</v>
       </c>
       <c r="H72" s="3">
-        <v>827400</v>
+        <v>1020000</v>
       </c>
       <c r="I72" s="3">
-        <v>733300</v>
+        <v>821800</v>
       </c>
       <c r="J72" s="3">
+        <v>728300</v>
+      </c>
+      <c r="K72" s="3">
         <v>638400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>578700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1781500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1960100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2183900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2222600</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2664600</v>
+        <v>2869700</v>
       </c>
       <c r="E76" s="3">
-        <v>2337400</v>
+        <v>2646500</v>
       </c>
       <c r="F76" s="3">
-        <v>1902300</v>
+        <v>2321500</v>
       </c>
       <c r="G76" s="3">
-        <v>2258900</v>
+        <v>1889400</v>
       </c>
       <c r="H76" s="3">
-        <v>2109300</v>
+        <v>2243500</v>
       </c>
       <c r="I76" s="3">
-        <v>2054100</v>
+        <v>2094900</v>
       </c>
       <c r="J76" s="3">
+        <v>2040100</v>
+      </c>
+      <c r="K76" s="3">
         <v>1990300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2154200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2221200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2649600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2591600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2849500</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>617900</v>
+        <v>361300</v>
       </c>
       <c r="E81" s="3">
-        <v>338100</v>
+        <v>613700</v>
       </c>
       <c r="F81" s="3">
-        <v>96300</v>
+        <v>335800</v>
       </c>
       <c r="G81" s="3">
-        <v>271000</v>
+        <v>95700</v>
       </c>
       <c r="H81" s="3">
-        <v>145300</v>
+        <v>269200</v>
       </c>
       <c r="I81" s="3">
-        <v>134000</v>
+        <v>144300</v>
       </c>
       <c r="J81" s="3">
+        <v>133100</v>
+      </c>
+      <c r="K81" s="3">
         <v>89200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>38700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-285500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-45800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-77200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,34 +3687,35 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300600</v>
+        <v>309900</v>
       </c>
       <c r="E83" s="3">
-        <v>273400</v>
+        <v>298600</v>
       </c>
       <c r="F83" s="3">
-        <v>265800</v>
+        <v>271500</v>
       </c>
       <c r="G83" s="3">
-        <v>260000</v>
+        <v>264000</v>
       </c>
       <c r="H83" s="3">
-        <v>202900</v>
+        <v>258300</v>
       </c>
       <c r="I83" s="3">
-        <v>206300</v>
+        <v>201500</v>
       </c>
       <c r="J83" s="3">
+        <v>204900</v>
+      </c>
+      <c r="K83" s="3">
         <v>208200</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
@@ -3525,15 +3723,18 @@
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>213700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>215900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>787600</v>
+        <v>443000</v>
       </c>
       <c r="E89" s="3">
-        <v>555500</v>
+        <v>782200</v>
       </c>
       <c r="F89" s="3">
-        <v>549100</v>
+        <v>551800</v>
       </c>
       <c r="G89" s="3">
-        <v>467600</v>
+        <v>545400</v>
       </c>
       <c r="H89" s="3">
-        <v>347600</v>
+        <v>464500</v>
       </c>
       <c r="I89" s="3">
-        <v>296300</v>
+        <v>345200</v>
       </c>
       <c r="J89" s="3">
+        <v>294300</v>
+      </c>
+      <c r="K89" s="3">
         <v>363200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>228000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>235100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>224600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>252000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>192500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-383600</v>
+        <v>-293500</v>
       </c>
       <c r="E91" s="3">
-        <v>-304400</v>
+        <v>-381000</v>
       </c>
       <c r="F91" s="3">
-        <v>-218800</v>
+        <v>-302300</v>
       </c>
       <c r="G91" s="3">
-        <v>-278000</v>
+        <v>-217300</v>
       </c>
       <c r="H91" s="3">
-        <v>-234900</v>
+        <v>-276100</v>
       </c>
       <c r="I91" s="3">
-        <v>-177600</v>
+        <v>-233300</v>
       </c>
       <c r="J91" s="3">
+        <v>-176400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-178000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-134900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-139000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-125400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-133900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-135200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,35 +4153,38 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-362100</v>
+        <v>-349000</v>
       </c>
       <c r="E94" s="3">
-        <v>-725400</v>
+        <v>-359700</v>
       </c>
       <c r="F94" s="3">
-        <v>-160900</v>
+        <v>-720500</v>
       </c>
       <c r="G94" s="3">
-        <v>-287400</v>
+        <v>-159800</v>
       </c>
       <c r="H94" s="3">
-        <v>-230300</v>
+        <v>-285400</v>
       </c>
       <c r="I94" s="3">
-        <v>-194500</v>
+        <v>-228700</v>
       </c>
       <c r="J94" s="3">
+        <v>-193100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-142700</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
@@ -3963,15 +4192,18 @@
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-251800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-99600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-91300</v>
+        <v>-102500</v>
       </c>
       <c r="E96" s="3">
-        <v>-73300</v>
+        <v>-90600</v>
       </c>
       <c r="F96" s="3">
-        <v>-73300</v>
+        <v>-72800</v>
       </c>
       <c r="G96" s="3">
-        <v>-62300</v>
+        <v>-72800</v>
       </c>
       <c r="H96" s="3">
-        <v>-37900</v>
+        <v>-61900</v>
       </c>
       <c r="I96" s="3">
-        <v>-34400</v>
+        <v>-37600</v>
       </c>
       <c r="J96" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-25500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-14600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-15100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-16200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-15200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-13800</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,35 +4397,38 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-488300</v>
+        <v>41900</v>
       </c>
       <c r="E100" s="3">
-        <v>-160600</v>
+        <v>-485000</v>
       </c>
       <c r="F100" s="3">
-        <v>199400</v>
+        <v>-159500</v>
       </c>
       <c r="G100" s="3">
-        <v>-219000</v>
+        <v>198000</v>
       </c>
       <c r="H100" s="3">
-        <v>-123700</v>
+        <v>-217500</v>
       </c>
       <c r="I100" s="3">
-        <v>-130800</v>
+        <v>-122900</v>
       </c>
       <c r="J100" s="3">
+        <v>-129900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-173200</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
@@ -4191,41 +4436,44 @@
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-273000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-31300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
@@ -4233,55 +4481,61 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-62900</v>
+        <v>126500</v>
       </c>
       <c r="E102" s="3">
-        <v>-328400</v>
+        <v>-62500</v>
       </c>
       <c r="F102" s="3">
-        <v>584700</v>
+        <v>-326200</v>
       </c>
       <c r="G102" s="3">
-        <v>-37300</v>
+        <v>580800</v>
       </c>
       <c r="H102" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-6700</v>
       </c>
-      <c r="I102" s="3">
-        <v>-30200</v>
-      </c>
       <c r="J102" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="K102" s="3">
         <v>45900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-234300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-241600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>299300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-272400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4565200</v>
+        <v>4678900</v>
       </c>
       <c r="E8" s="3">
-        <v>5378400</v>
+        <v>5512200</v>
       </c>
       <c r="F8" s="3">
-        <v>4291800</v>
+        <v>4398600</v>
       </c>
       <c r="G8" s="3">
-        <v>3625300</v>
+        <v>3715600</v>
       </c>
       <c r="H8" s="3">
-        <v>3746000</v>
+        <v>3839300</v>
       </c>
       <c r="I8" s="3">
-        <v>3571800</v>
+        <v>3660700</v>
       </c>
       <c r="J8" s="3">
-        <v>3371500</v>
+        <v>3455400</v>
       </c>
       <c r="K8" s="3">
         <v>3235800</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2822500</v>
+        <v>2892800</v>
       </c>
       <c r="E9" s="3">
-        <v>3273900</v>
+        <v>3355400</v>
       </c>
       <c r="F9" s="3">
-        <v>2736400</v>
+        <v>2804600</v>
       </c>
       <c r="G9" s="3">
-        <v>2340900</v>
+        <v>2399200</v>
       </c>
       <c r="H9" s="3">
-        <v>2390000</v>
+        <v>2449500</v>
       </c>
       <c r="I9" s="3">
-        <v>2319500</v>
+        <v>2377300</v>
       </c>
       <c r="J9" s="3">
-        <v>2262700</v>
+        <v>2319000</v>
       </c>
       <c r="K9" s="3">
         <v>2188400</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1742700</v>
+        <v>1786100</v>
       </c>
       <c r="E10" s="3">
-        <v>2104400</v>
+        <v>2156800</v>
       </c>
       <c r="F10" s="3">
-        <v>1555300</v>
+        <v>1594100</v>
       </c>
       <c r="G10" s="3">
-        <v>1284400</v>
+        <v>1316300</v>
       </c>
       <c r="H10" s="3">
-        <v>1356000</v>
+        <v>1389800</v>
       </c>
       <c r="I10" s="3">
-        <v>1252300</v>
+        <v>1283400</v>
       </c>
       <c r="J10" s="3">
-        <v>1108800</v>
+        <v>1136400</v>
       </c>
       <c r="K10" s="3">
         <v>1047400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>18500</v>
+        <v>19000</v>
       </c>
       <c r="E14" s="3">
-        <v>20400</v>
+        <v>20900</v>
       </c>
       <c r="F14" s="3">
-        <v>21100</v>
+        <v>21600</v>
       </c>
       <c r="G14" s="3">
-        <v>127000</v>
+        <v>130100</v>
       </c>
       <c r="H14" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I14" s="3">
-        <v>11600</v>
+        <v>11900</v>
       </c>
       <c r="J14" s="3">
-        <v>16800</v>
+        <v>17200</v>
       </c>
       <c r="K14" s="3">
         <v>7800</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>103800</v>
+        <v>106400</v>
       </c>
       <c r="E15" s="3">
-        <v>132700</v>
+        <v>136000</v>
       </c>
       <c r="F15" s="3">
-        <v>113300</v>
+        <v>116100</v>
       </c>
       <c r="G15" s="3">
-        <v>212400</v>
+        <v>217700</v>
       </c>
       <c r="H15" s="3">
-        <v>84000</v>
+        <v>86100</v>
       </c>
       <c r="I15" s="3">
-        <v>64900</v>
+        <v>66500</v>
       </c>
       <c r="J15" s="3">
-        <v>94700</v>
+        <v>97100</v>
       </c>
       <c r="K15" s="3">
         <v>69700</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4049200</v>
+        <v>4150000</v>
       </c>
       <c r="E17" s="3">
-        <v>4599400</v>
+        <v>4713900</v>
       </c>
       <c r="F17" s="3">
-        <v>3846900</v>
+        <v>3942700</v>
       </c>
       <c r="G17" s="3">
-        <v>3422500</v>
+        <v>3507700</v>
       </c>
       <c r="H17" s="3">
-        <v>3355800</v>
+        <v>3439300</v>
       </c>
       <c r="I17" s="3">
-        <v>3315100</v>
+        <v>3397600</v>
       </c>
       <c r="J17" s="3">
-        <v>3178400</v>
+        <v>3257600</v>
       </c>
       <c r="K17" s="3">
         <v>3028500</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>516100</v>
+        <v>528900</v>
       </c>
       <c r="E18" s="3">
-        <v>778900</v>
+        <v>798300</v>
       </c>
       <c r="F18" s="3">
-        <v>444900</v>
+        <v>456000</v>
       </c>
       <c r="G18" s="3">
-        <v>202800</v>
+        <v>207900</v>
       </c>
       <c r="H18" s="3">
-        <v>390200</v>
+        <v>399900</v>
       </c>
       <c r="I18" s="3">
-        <v>256700</v>
+        <v>263100</v>
       </c>
       <c r="J18" s="3">
-        <v>193000</v>
+        <v>197800</v>
       </c>
       <c r="K18" s="3">
         <v>207300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21900</v>
+        <v>22500</v>
       </c>
       <c r="E20" s="3">
-        <v>16000</v>
+        <v>16400</v>
       </c>
       <c r="F20" s="3">
         <v>1600</v>
       </c>
       <c r="G20" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="H20" s="3">
-        <v>-7400</v>
+        <v>-7500</v>
       </c>
       <c r="I20" s="3">
         <v>-1800</v>
       </c>
       <c r="J20" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="K20" s="3">
         <v>4300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>846000</v>
+        <v>869000</v>
       </c>
       <c r="E21" s="3">
-        <v>1091600</v>
+        <v>1120600</v>
       </c>
       <c r="F21" s="3">
-        <v>716200</v>
+        <v>735800</v>
       </c>
       <c r="G21" s="3">
-        <v>462000</v>
+        <v>475200</v>
       </c>
       <c r="H21" s="3">
-        <v>639500</v>
+        <v>657000</v>
       </c>
       <c r="I21" s="3">
-        <v>455100</v>
+        <v>467700</v>
       </c>
       <c r="J21" s="3">
-        <v>402000</v>
+        <v>413300</v>
       </c>
       <c r="K21" s="3">
         <v>421000</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>79400</v>
+        <v>81400</v>
       </c>
       <c r="E22" s="3">
-        <v>51000</v>
+        <v>52300</v>
       </c>
       <c r="F22" s="3">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="G22" s="3">
-        <v>38900</v>
+        <v>39900</v>
       </c>
       <c r="H22" s="3">
-        <v>42100</v>
+        <v>43200</v>
       </c>
       <c r="I22" s="3">
-        <v>43800</v>
+        <v>44900</v>
       </c>
       <c r="J22" s="3">
-        <v>41800</v>
+        <v>42900</v>
       </c>
       <c r="K22" s="3">
         <v>39100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>458600</v>
+        <v>470000</v>
       </c>
       <c r="E23" s="3">
-        <v>743900</v>
+        <v>762400</v>
       </c>
       <c r="F23" s="3">
-        <v>404500</v>
+        <v>414500</v>
       </c>
       <c r="G23" s="3">
-        <v>160800</v>
+        <v>164800</v>
       </c>
       <c r="H23" s="3">
-        <v>340700</v>
+        <v>349200</v>
       </c>
       <c r="I23" s="3">
-        <v>211100</v>
+        <v>216400</v>
       </c>
       <c r="J23" s="3">
-        <v>156600</v>
+        <v>160500</v>
       </c>
       <c r="K23" s="3">
         <v>172500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>96400</v>
+        <v>98800</v>
       </c>
       <c r="E24" s="3">
-        <v>129500</v>
+        <v>132700</v>
       </c>
       <c r="F24" s="3">
-        <v>67200</v>
+        <v>68900</v>
       </c>
       <c r="G24" s="3">
-        <v>52800</v>
+        <v>54100</v>
       </c>
       <c r="H24" s="3">
-        <v>56700</v>
+        <v>58200</v>
       </c>
       <c r="I24" s="3">
-        <v>52400</v>
+        <v>53700</v>
       </c>
       <c r="J24" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="K24" s="3">
         <v>47000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>362200</v>
+        <v>371200</v>
       </c>
       <c r="E26" s="3">
-        <v>614400</v>
+        <v>629700</v>
       </c>
       <c r="F26" s="3">
-        <v>337300</v>
+        <v>345600</v>
       </c>
       <c r="G26" s="3">
-        <v>108000</v>
+        <v>110700</v>
       </c>
       <c r="H26" s="3">
-        <v>284000</v>
+        <v>291000</v>
       </c>
       <c r="I26" s="3">
-        <v>158700</v>
+        <v>162700</v>
       </c>
       <c r="J26" s="3">
-        <v>152000</v>
+        <v>155800</v>
       </c>
       <c r="K26" s="3">
         <v>125500</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>361300</v>
+        <v>370300</v>
       </c>
       <c r="E27" s="3">
-        <v>613700</v>
+        <v>629000</v>
       </c>
       <c r="F27" s="3">
-        <v>335800</v>
+        <v>344100</v>
       </c>
       <c r="G27" s="3">
-        <v>95700</v>
+        <v>98100</v>
       </c>
       <c r="H27" s="3">
-        <v>269200</v>
+        <v>275900</v>
       </c>
       <c r="I27" s="3">
-        <v>144300</v>
+        <v>147900</v>
       </c>
       <c r="J27" s="3">
-        <v>133100</v>
+        <v>136400</v>
       </c>
       <c r="K27" s="3">
         <v>89200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21900</v>
+        <v>-22500</v>
       </c>
       <c r="E32" s="3">
-        <v>-16000</v>
+        <v>-16400</v>
       </c>
       <c r="F32" s="3">
         <v>-1600</v>
       </c>
       <c r="G32" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="H32" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="I32" s="3">
         <v>1800</v>
       </c>
       <c r="J32" s="3">
-        <v>-5400</v>
+        <v>-5500</v>
       </c>
       <c r="K32" s="3">
         <v>-4300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>361300</v>
+        <v>370300</v>
       </c>
       <c r="E33" s="3">
-        <v>613700</v>
+        <v>629000</v>
       </c>
       <c r="F33" s="3">
-        <v>335800</v>
+        <v>344100</v>
       </c>
       <c r="G33" s="3">
-        <v>95700</v>
+        <v>98100</v>
       </c>
       <c r="H33" s="3">
-        <v>269200</v>
+        <v>275900</v>
       </c>
       <c r="I33" s="3">
-        <v>144300</v>
+        <v>147900</v>
       </c>
       <c r="J33" s="3">
-        <v>133100</v>
+        <v>136400</v>
       </c>
       <c r="K33" s="3">
         <v>89200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>361300</v>
+        <v>370300</v>
       </c>
       <c r="E35" s="3">
-        <v>613700</v>
+        <v>629000</v>
       </c>
       <c r="F35" s="3">
-        <v>335800</v>
+        <v>344100</v>
       </c>
       <c r="G35" s="3">
-        <v>95700</v>
+        <v>98100</v>
       </c>
       <c r="H35" s="3">
-        <v>269200</v>
+        <v>275900</v>
       </c>
       <c r="I35" s="3">
-        <v>144300</v>
+        <v>147900</v>
       </c>
       <c r="J35" s="3">
-        <v>133100</v>
+        <v>136400</v>
       </c>
       <c r="K35" s="3">
         <v>89200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>447500</v>
+        <v>458700</v>
       </c>
       <c r="E41" s="3">
-        <v>324200</v>
+        <v>332300</v>
       </c>
       <c r="F41" s="3">
-        <v>393700</v>
+        <v>403500</v>
       </c>
       <c r="G41" s="3">
-        <v>719900</v>
+        <v>737800</v>
       </c>
       <c r="H41" s="3">
-        <v>139100</v>
+        <v>142600</v>
       </c>
       <c r="I41" s="3">
-        <v>176200</v>
+        <v>180600</v>
       </c>
       <c r="J41" s="3">
-        <v>182900</v>
+        <v>187500</v>
       </c>
       <c r="K41" s="3">
         <v>214400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="E42" s="3">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="F42" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H42" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I42" s="3">
         <v>6800</v>
       </c>
-      <c r="G42" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H42" s="3">
-        <v>7400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>6600</v>
-      </c>
       <c r="J42" s="3">
-        <v>85400</v>
+        <v>87500</v>
       </c>
       <c r="K42" s="3">
         <v>57400</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>490700</v>
+        <v>502900</v>
       </c>
       <c r="E43" s="3">
-        <v>563700</v>
+        <v>577700</v>
       </c>
       <c r="F43" s="3">
-        <v>542700</v>
+        <v>556200</v>
       </c>
       <c r="G43" s="3">
-        <v>366200</v>
+        <v>375300</v>
       </c>
       <c r="H43" s="3">
-        <v>380100</v>
+        <v>389500</v>
       </c>
       <c r="I43" s="3">
-        <v>366900</v>
+        <v>376100</v>
       </c>
       <c r="J43" s="3">
-        <v>320700</v>
+        <v>328700</v>
       </c>
       <c r="K43" s="3">
         <v>286200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1246900</v>
+        <v>1277900</v>
       </c>
       <c r="E44" s="3">
-        <v>1119800</v>
+        <v>1147700</v>
       </c>
       <c r="F44" s="3">
-        <v>954600</v>
+        <v>978300</v>
       </c>
       <c r="G44" s="3">
-        <v>787900</v>
+        <v>807500</v>
       </c>
       <c r="H44" s="3">
-        <v>894400</v>
+        <v>916600</v>
       </c>
       <c r="I44" s="3">
-        <v>823100</v>
+        <v>843600</v>
       </c>
       <c r="J44" s="3">
-        <v>801400</v>
+        <v>821400</v>
       </c>
       <c r="K44" s="3">
         <v>781600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>50500</v>
+        <v>51800</v>
       </c>
       <c r="E45" s="3">
-        <v>58000</v>
+        <v>59400</v>
       </c>
       <c r="F45" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3">
-        <v>12900</v>
+        <v>13200</v>
       </c>
       <c r="H45" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="I45" s="3">
-        <v>10300</v>
+        <v>10600</v>
       </c>
       <c r="J45" s="3">
-        <v>24600</v>
+        <v>25200</v>
       </c>
       <c r="K45" s="3">
         <v>22100</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2242200</v>
+        <v>2298000</v>
       </c>
       <c r="E46" s="3">
-        <v>2071700</v>
+        <v>2123300</v>
       </c>
       <c r="F46" s="3">
-        <v>1902700</v>
+        <v>1950100</v>
       </c>
       <c r="G46" s="3">
-        <v>1893900</v>
+        <v>1941100</v>
       </c>
       <c r="H46" s="3">
-        <v>1424300</v>
+        <v>1459700</v>
       </c>
       <c r="I46" s="3">
-        <v>1383300</v>
+        <v>1417700</v>
       </c>
       <c r="J46" s="3">
-        <v>1415000</v>
+        <v>1450200</v>
       </c>
       <c r="K46" s="3">
         <v>1361700</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>63500</v>
+        <v>65100</v>
       </c>
       <c r="E47" s="3">
-        <v>47300</v>
+        <v>48500</v>
       </c>
       <c r="F47" s="3">
-        <v>43500</v>
+        <v>44600</v>
       </c>
       <c r="G47" s="3">
-        <v>67400</v>
+        <v>69100</v>
       </c>
       <c r="H47" s="3">
-        <v>56300</v>
+        <v>57700</v>
       </c>
       <c r="I47" s="3">
-        <v>56800</v>
+        <v>58200</v>
       </c>
       <c r="J47" s="3">
-        <v>30300</v>
+        <v>31100</v>
       </c>
       <c r="K47" s="3">
         <v>29900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2604100</v>
+        <v>2668900</v>
       </c>
       <c r="E48" s="3">
-        <v>2493000</v>
+        <v>2555000</v>
       </c>
       <c r="F48" s="3">
-        <v>2334400</v>
+        <v>2392500</v>
       </c>
       <c r="G48" s="3">
-        <v>1951400</v>
+        <v>2000000</v>
       </c>
       <c r="H48" s="3">
-        <v>2097100</v>
+        <v>2149300</v>
       </c>
       <c r="I48" s="3">
-        <v>1774800</v>
+        <v>1819000</v>
       </c>
       <c r="J48" s="3">
-        <v>1715600</v>
+        <v>1758300</v>
       </c>
       <c r="K48" s="3">
         <v>1795900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>923900</v>
+        <v>946900</v>
       </c>
       <c r="E49" s="3">
-        <v>915100</v>
+        <v>937900</v>
       </c>
       <c r="F49" s="3">
-        <v>926600</v>
+        <v>949600</v>
       </c>
       <c r="G49" s="3">
-        <v>697700</v>
+        <v>715000</v>
       </c>
       <c r="H49" s="3">
-        <v>821700</v>
+        <v>842200</v>
       </c>
       <c r="I49" s="3">
-        <v>770200</v>
+        <v>789400</v>
       </c>
       <c r="J49" s="3">
-        <v>746700</v>
+        <v>765200</v>
       </c>
       <c r="K49" s="3">
         <v>751300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>76200</v>
+        <v>78100</v>
       </c>
       <c r="E52" s="3">
-        <v>91700</v>
+        <v>94000</v>
       </c>
       <c r="F52" s="3">
-        <v>92400</v>
+        <v>94700</v>
       </c>
       <c r="G52" s="3">
-        <v>65800</v>
+        <v>67500</v>
       </c>
       <c r="H52" s="3">
-        <v>66700</v>
+        <v>68300</v>
       </c>
       <c r="I52" s="3">
-        <v>59900</v>
+        <v>61400</v>
       </c>
       <c r="J52" s="3">
-        <v>47600</v>
+        <v>48800</v>
       </c>
       <c r="K52" s="3">
         <v>18900</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5909900</v>
+        <v>6057000</v>
       </c>
       <c r="E54" s="3">
-        <v>5618800</v>
+        <v>5758700</v>
       </c>
       <c r="F54" s="3">
-        <v>5299500</v>
+        <v>5431400</v>
       </c>
       <c r="G54" s="3">
-        <v>4676200</v>
+        <v>4792600</v>
       </c>
       <c r="H54" s="3">
-        <v>4466100</v>
+        <v>4577300</v>
       </c>
       <c r="I54" s="3">
-        <v>4045000</v>
+        <v>4145600</v>
       </c>
       <c r="J54" s="3">
-        <v>3955200</v>
+        <v>4053700</v>
       </c>
       <c r="K54" s="3">
         <v>3957600</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>356700</v>
+        <v>365600</v>
       </c>
       <c r="E57" s="3">
-        <v>475000</v>
+        <v>486900</v>
       </c>
       <c r="F57" s="3">
-        <v>457200</v>
+        <v>468600</v>
       </c>
       <c r="G57" s="3">
-        <v>324100</v>
+        <v>332100</v>
       </c>
       <c r="H57" s="3">
-        <v>363600</v>
+        <v>372600</v>
       </c>
       <c r="I57" s="3">
-        <v>353300</v>
+        <v>362100</v>
       </c>
       <c r="J57" s="3">
-        <v>347500</v>
+        <v>356100</v>
       </c>
       <c r="K57" s="3">
         <v>329400</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>461000</v>
+        <v>472500</v>
       </c>
       <c r="E58" s="3">
-        <v>223800</v>
+        <v>229400</v>
       </c>
       <c r="F58" s="3">
-        <v>230200</v>
+        <v>235900</v>
       </c>
       <c r="G58" s="3">
-        <v>473000</v>
+        <v>484800</v>
       </c>
       <c r="H58" s="3">
-        <v>497400</v>
+        <v>509700</v>
       </c>
       <c r="I58" s="3">
-        <v>137100</v>
+        <v>140600</v>
       </c>
       <c r="J58" s="3">
-        <v>346600</v>
+        <v>355200</v>
       </c>
       <c r="K58" s="3">
         <v>435200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>509300</v>
+        <v>522000</v>
       </c>
       <c r="E59" s="3">
-        <v>593300</v>
+        <v>608100</v>
       </c>
       <c r="F59" s="3">
-        <v>493700</v>
+        <v>506000</v>
       </c>
       <c r="G59" s="3">
-        <v>409000</v>
+        <v>419200</v>
       </c>
       <c r="H59" s="3">
-        <v>390500</v>
+        <v>400200</v>
       </c>
       <c r="I59" s="3">
-        <v>369100</v>
+        <v>378300</v>
       </c>
       <c r="J59" s="3">
-        <v>327800</v>
+        <v>336000</v>
       </c>
       <c r="K59" s="3">
         <v>301100</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1327100</v>
+        <v>1360100</v>
       </c>
       <c r="E60" s="3">
-        <v>1292200</v>
+        <v>1324400</v>
       </c>
       <c r="F60" s="3">
-        <v>1181100</v>
+        <v>1210500</v>
       </c>
       <c r="G60" s="3">
-        <v>1206100</v>
+        <v>1236100</v>
       </c>
       <c r="H60" s="3">
-        <v>1251400</v>
+        <v>1282500</v>
       </c>
       <c r="I60" s="3">
-        <v>859600</v>
+        <v>881000</v>
       </c>
       <c r="J60" s="3">
-        <v>1021900</v>
+        <v>1047300</v>
       </c>
       <c r="K60" s="3">
         <v>1065600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1377400</v>
+        <v>1411700</v>
       </c>
       <c r="E61" s="3">
-        <v>1345500</v>
+        <v>1379000</v>
       </c>
       <c r="F61" s="3">
-        <v>1433100</v>
+        <v>1468800</v>
       </c>
       <c r="G61" s="3">
-        <v>1253400</v>
+        <v>1284600</v>
       </c>
       <c r="H61" s="3">
-        <v>622700</v>
+        <v>638300</v>
       </c>
       <c r="I61" s="3">
-        <v>767900</v>
+        <v>787000</v>
       </c>
       <c r="J61" s="3">
-        <v>533800</v>
+        <v>547100</v>
       </c>
       <c r="K61" s="3">
         <v>523800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>320800</v>
+        <v>328800</v>
       </c>
       <c r="E62" s="3">
-        <v>317000</v>
+        <v>324900</v>
       </c>
       <c r="F62" s="3">
-        <v>362800</v>
+        <v>371800</v>
       </c>
       <c r="G62" s="3">
-        <v>326600</v>
+        <v>334700</v>
       </c>
       <c r="H62" s="3">
-        <v>347500</v>
+        <v>356200</v>
       </c>
       <c r="I62" s="3">
-        <v>321900</v>
+        <v>329900</v>
       </c>
       <c r="J62" s="3">
-        <v>334000</v>
+        <v>342400</v>
       </c>
       <c r="K62" s="3">
         <v>356300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3040200</v>
+        <v>3115800</v>
       </c>
       <c r="E66" s="3">
-        <v>2972400</v>
+        <v>3046300</v>
       </c>
       <c r="F66" s="3">
-        <v>2978000</v>
+        <v>3052100</v>
       </c>
       <c r="G66" s="3">
-        <v>2786800</v>
+        <v>2856200</v>
       </c>
       <c r="H66" s="3">
-        <v>2222600</v>
+        <v>2277900</v>
       </c>
       <c r="I66" s="3">
-        <v>1950000</v>
+        <v>1998600</v>
       </c>
       <c r="J66" s="3">
-        <v>1915100</v>
+        <v>1962800</v>
       </c>
       <c r="K66" s="3">
         <v>1967300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2076600</v>
+        <v>2128300</v>
       </c>
       <c r="E72" s="3">
-        <v>1813300</v>
+        <v>1858400</v>
       </c>
       <c r="F72" s="3">
-        <v>1285700</v>
+        <v>1317700</v>
       </c>
       <c r="G72" s="3">
-        <v>1022500</v>
+        <v>1048000</v>
       </c>
       <c r="H72" s="3">
-        <v>1020000</v>
+        <v>1045400</v>
       </c>
       <c r="I72" s="3">
-        <v>821800</v>
+        <v>842200</v>
       </c>
       <c r="J72" s="3">
-        <v>728300</v>
+        <v>746500</v>
       </c>
       <c r="K72" s="3">
         <v>638400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2869700</v>
+        <v>2941200</v>
       </c>
       <c r="E76" s="3">
-        <v>2646500</v>
+        <v>2712300</v>
       </c>
       <c r="F76" s="3">
-        <v>2321500</v>
+        <v>2379300</v>
       </c>
       <c r="G76" s="3">
-        <v>1889400</v>
+        <v>1936400</v>
       </c>
       <c r="H76" s="3">
-        <v>2243500</v>
+        <v>2299400</v>
       </c>
       <c r="I76" s="3">
-        <v>2094900</v>
+        <v>2147100</v>
       </c>
       <c r="J76" s="3">
-        <v>2040100</v>
+        <v>2090900</v>
       </c>
       <c r="K76" s="3">
         <v>1990300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>361300</v>
+        <v>370300</v>
       </c>
       <c r="E81" s="3">
-        <v>613700</v>
+        <v>629000</v>
       </c>
       <c r="F81" s="3">
-        <v>335800</v>
+        <v>344100</v>
       </c>
       <c r="G81" s="3">
-        <v>95700</v>
+        <v>98100</v>
       </c>
       <c r="H81" s="3">
-        <v>269200</v>
+        <v>275900</v>
       </c>
       <c r="I81" s="3">
-        <v>144300</v>
+        <v>147900</v>
       </c>
       <c r="J81" s="3">
-        <v>133100</v>
+        <v>136400</v>
       </c>
       <c r="K81" s="3">
         <v>89200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>309900</v>
+        <v>317600</v>
       </c>
       <c r="E83" s="3">
-        <v>298600</v>
+        <v>306000</v>
       </c>
       <c r="F83" s="3">
-        <v>271500</v>
+        <v>278300</v>
       </c>
       <c r="G83" s="3">
-        <v>264000</v>
+        <v>270600</v>
       </c>
       <c r="H83" s="3">
-        <v>258300</v>
+        <v>264700</v>
       </c>
       <c r="I83" s="3">
-        <v>201500</v>
+        <v>206500</v>
       </c>
       <c r="J83" s="3">
-        <v>204900</v>
+        <v>210000</v>
       </c>
       <c r="K83" s="3">
         <v>208200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>443000</v>
+        <v>454100</v>
       </c>
       <c r="E89" s="3">
-        <v>782200</v>
+        <v>801700</v>
       </c>
       <c r="F89" s="3">
-        <v>551800</v>
+        <v>565500</v>
       </c>
       <c r="G89" s="3">
-        <v>545400</v>
+        <v>559000</v>
       </c>
       <c r="H89" s="3">
-        <v>464500</v>
+        <v>476000</v>
       </c>
       <c r="I89" s="3">
-        <v>345200</v>
+        <v>353800</v>
       </c>
       <c r="J89" s="3">
-        <v>294300</v>
+        <v>301600</v>
       </c>
       <c r="K89" s="3">
         <v>363200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-293500</v>
+        <v>-300800</v>
       </c>
       <c r="E91" s="3">
-        <v>-381000</v>
+        <v>-390500</v>
       </c>
       <c r="F91" s="3">
-        <v>-302300</v>
+        <v>-309900</v>
       </c>
       <c r="G91" s="3">
-        <v>-217300</v>
+        <v>-222700</v>
       </c>
       <c r="H91" s="3">
-        <v>-276100</v>
+        <v>-283000</v>
       </c>
       <c r="I91" s="3">
-        <v>-233300</v>
+        <v>-239100</v>
       </c>
       <c r="J91" s="3">
-        <v>-176400</v>
+        <v>-180700</v>
       </c>
       <c r="K91" s="3">
         <v>-178000</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-349000</v>
+        <v>-357700</v>
       </c>
       <c r="E94" s="3">
-        <v>-359700</v>
+        <v>-368600</v>
       </c>
       <c r="F94" s="3">
-        <v>-720500</v>
+        <v>-738400</v>
       </c>
       <c r="G94" s="3">
-        <v>-159800</v>
+        <v>-163700</v>
       </c>
       <c r="H94" s="3">
-        <v>-285400</v>
+        <v>-292500</v>
       </c>
       <c r="I94" s="3">
-        <v>-228700</v>
+        <v>-234400</v>
       </c>
       <c r="J94" s="3">
-        <v>-193100</v>
+        <v>-197900</v>
       </c>
       <c r="K94" s="3">
         <v>-142700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-102500</v>
+        <v>-105100</v>
       </c>
       <c r="E96" s="3">
-        <v>-90600</v>
+        <v>-92900</v>
       </c>
       <c r="F96" s="3">
-        <v>-72800</v>
+        <v>-74600</v>
       </c>
       <c r="G96" s="3">
-        <v>-72800</v>
+        <v>-74600</v>
       </c>
       <c r="H96" s="3">
-        <v>-61900</v>
+        <v>-63500</v>
       </c>
       <c r="I96" s="3">
-        <v>-37600</v>
+        <v>-38600</v>
       </c>
       <c r="J96" s="3">
-        <v>-34100</v>
+        <v>-35000</v>
       </c>
       <c r="K96" s="3">
         <v>-25500</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>41900</v>
+        <v>42900</v>
       </c>
       <c r="E100" s="3">
-        <v>-485000</v>
+        <v>-497100</v>
       </c>
       <c r="F100" s="3">
-        <v>-159500</v>
+        <v>-163500</v>
       </c>
       <c r="G100" s="3">
-        <v>198000</v>
+        <v>203000</v>
       </c>
       <c r="H100" s="3">
-        <v>-217500</v>
+        <v>-222900</v>
       </c>
       <c r="I100" s="3">
-        <v>-122900</v>
+        <v>-125900</v>
       </c>
       <c r="J100" s="3">
-        <v>-129900</v>
+        <v>-133100</v>
       </c>
       <c r="K100" s="3">
         <v>-173200</v>
@@ -4452,7 +4452,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-9400</v>
+        <v>-9700</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
@@ -4461,13 +4461,13 @@
         <v>2100</v>
       </c>
       <c r="G101" s="3">
-        <v>-2900</v>
+        <v>-3000</v>
       </c>
       <c r="H101" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I101" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="J101" s="3">
         <v>-1300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>126500</v>
+        <v>129600</v>
       </c>
       <c r="E102" s="3">
-        <v>-62500</v>
+        <v>-64100</v>
       </c>
       <c r="F102" s="3">
-        <v>-326200</v>
+        <v>-334300</v>
       </c>
       <c r="G102" s="3">
-        <v>580800</v>
+        <v>595200</v>
       </c>
       <c r="H102" s="3">
-        <v>-37100</v>
+        <v>-38000</v>
       </c>
       <c r="I102" s="3">
-        <v>-6700</v>
+        <v>-6800</v>
       </c>
       <c r="J102" s="3">
-        <v>-30000</v>
+        <v>-30700</v>
       </c>
       <c r="K102" s="3">
         <v>45900</v>

--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>WBRBY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4678900</v>
+        <v>4669300</v>
       </c>
       <c r="E8" s="3">
-        <v>5512200</v>
+        <v>5318700</v>
       </c>
       <c r="F8" s="3">
-        <v>4398600</v>
+        <v>4516400</v>
       </c>
       <c r="G8" s="3">
-        <v>3715600</v>
+        <v>4103500</v>
       </c>
       <c r="H8" s="3">
-        <v>3839300</v>
+        <v>3889900</v>
       </c>
       <c r="I8" s="3">
-        <v>3660700</v>
+        <v>3784200</v>
       </c>
       <c r="J8" s="3">
-        <v>3455400</v>
+        <v>3746000</v>
       </c>
       <c r="K8" s="3">
         <v>3235800</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2892800</v>
+        <v>2886800</v>
       </c>
       <c r="E9" s="3">
-        <v>3355400</v>
+        <v>3237600</v>
       </c>
       <c r="F9" s="3">
-        <v>2804600</v>
+        <v>2879700</v>
       </c>
       <c r="G9" s="3">
-        <v>2399200</v>
+        <v>2649700</v>
       </c>
       <c r="H9" s="3">
-        <v>2449500</v>
+        <v>2481800</v>
       </c>
       <c r="I9" s="3">
-        <v>2377300</v>
+        <v>2457400</v>
       </c>
       <c r="J9" s="3">
-        <v>2319000</v>
+        <v>2514100</v>
       </c>
       <c r="K9" s="3">
         <v>2188400</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1786100</v>
+        <v>1782500</v>
       </c>
       <c r="E10" s="3">
-        <v>2156800</v>
+        <v>2081100</v>
       </c>
       <c r="F10" s="3">
-        <v>1594100</v>
+        <v>1636800</v>
       </c>
       <c r="G10" s="3">
-        <v>1316300</v>
+        <v>1453800</v>
       </c>
       <c r="H10" s="3">
-        <v>1389800</v>
+        <v>1408100</v>
       </c>
       <c r="I10" s="3">
-        <v>1283400</v>
+        <v>1326700</v>
       </c>
       <c r="J10" s="3">
-        <v>1136400</v>
+        <v>1232000</v>
       </c>
       <c r="K10" s="3">
         <v>1047400</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>19300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>21300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>19600</v>
+      </c>
+      <c r="I12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>13200</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>19000</v>
+        <v>7000</v>
       </c>
       <c r="E14" s="3">
-        <v>20900</v>
+        <v>-7400</v>
       </c>
       <c r="F14" s="3">
-        <v>21600</v>
+        <v>4900</v>
       </c>
       <c r="G14" s="3">
-        <v>130100</v>
+        <v>128500</v>
       </c>
       <c r="H14" s="3">
-        <v>1800</v>
+        <v>-14300</v>
       </c>
       <c r="I14" s="3">
-        <v>11900</v>
+        <v>9700</v>
       </c>
       <c r="J14" s="3">
-        <v>17200</v>
+        <v>18600</v>
       </c>
       <c r="K14" s="3">
         <v>7800</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>106400</v>
+        <v>248000</v>
       </c>
       <c r="E15" s="3">
-        <v>136000</v>
+        <v>229200</v>
       </c>
       <c r="F15" s="3">
-        <v>116100</v>
+        <v>227900</v>
       </c>
       <c r="G15" s="3">
-        <v>217700</v>
+        <v>241200</v>
       </c>
       <c r="H15" s="3">
-        <v>86100</v>
+        <v>218200</v>
       </c>
       <c r="I15" s="3">
-        <v>66500</v>
+        <v>213500</v>
       </c>
       <c r="J15" s="3">
-        <v>97100</v>
+        <v>227700</v>
       </c>
       <c r="K15" s="3">
         <v>69700</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4150000</v>
+        <v>4140600</v>
       </c>
       <c r="E17" s="3">
-        <v>4713900</v>
+        <v>4561300</v>
       </c>
       <c r="F17" s="3">
-        <v>3942700</v>
+        <v>4044700</v>
       </c>
       <c r="G17" s="3">
-        <v>3507700</v>
+        <v>3746600</v>
       </c>
       <c r="H17" s="3">
-        <v>3439300</v>
+        <v>3500600</v>
       </c>
       <c r="I17" s="3">
-        <v>3397600</v>
+        <v>3503500</v>
       </c>
       <c r="J17" s="3">
-        <v>3257600</v>
+        <v>3512900</v>
       </c>
       <c r="K17" s="3">
         <v>3028500</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>528900</v>
+        <v>528800</v>
       </c>
       <c r="E18" s="3">
-        <v>798300</v>
+        <v>757400</v>
       </c>
       <c r="F18" s="3">
-        <v>456000</v>
+        <v>471700</v>
       </c>
       <c r="G18" s="3">
-        <v>207900</v>
+        <v>356900</v>
       </c>
       <c r="H18" s="3">
-        <v>399900</v>
+        <v>389300</v>
       </c>
       <c r="I18" s="3">
-        <v>263100</v>
+        <v>280600</v>
       </c>
       <c r="J18" s="3">
-        <v>197800</v>
+        <v>233200</v>
       </c>
       <c r="K18" s="3">
         <v>207300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>22500</v>
+        <v>-5000</v>
       </c>
       <c r="E20" s="3">
-        <v>16400</v>
+        <v>-13600</v>
       </c>
       <c r="F20" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="G20" s="3">
-        <v>-3200</v>
+        <v>6100</v>
       </c>
       <c r="H20" s="3">
-        <v>-7500</v>
+        <v>9700</v>
       </c>
       <c r="I20" s="3">
-        <v>-1800</v>
+        <v>7100</v>
       </c>
       <c r="J20" s="3">
-        <v>5500</v>
+        <v>-1400</v>
       </c>
       <c r="K20" s="3">
         <v>4300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>869000</v>
+        <v>781800</v>
       </c>
       <c r="E21" s="3">
-        <v>1120600</v>
+        <v>1000300</v>
       </c>
       <c r="F21" s="3">
-        <v>735800</v>
+        <v>698600</v>
       </c>
       <c r="G21" s="3">
-        <v>475200</v>
+        <v>592100</v>
       </c>
       <c r="H21" s="3">
-        <v>657000</v>
+        <v>597800</v>
       </c>
       <c r="I21" s="3">
-        <v>467700</v>
+        <v>487000</v>
       </c>
       <c r="J21" s="3">
-        <v>413300</v>
+        <v>462300</v>
       </c>
       <c r="K21" s="3">
         <v>421000</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>81400</v>
+        <v>81200</v>
       </c>
       <c r="E22" s="3">
-        <v>52300</v>
+        <v>50500</v>
       </c>
       <c r="F22" s="3">
-        <v>43000</v>
+        <v>44100</v>
       </c>
       <c r="G22" s="3">
-        <v>39900</v>
+        <v>44000</v>
       </c>
       <c r="H22" s="3">
-        <v>43200</v>
+        <v>43700</v>
       </c>
       <c r="I22" s="3">
-        <v>44900</v>
+        <v>46400</v>
       </c>
       <c r="J22" s="3">
-        <v>42900</v>
+        <v>50600</v>
       </c>
       <c r="K22" s="3">
         <v>39100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>470000</v>
+        <v>469000</v>
       </c>
       <c r="E23" s="3">
-        <v>762400</v>
+        <v>735600</v>
       </c>
       <c r="F23" s="3">
-        <v>414500</v>
+        <v>425600</v>
       </c>
       <c r="G23" s="3">
-        <v>164800</v>
+        <v>182000</v>
       </c>
       <c r="H23" s="3">
-        <v>349200</v>
+        <v>353800</v>
       </c>
       <c r="I23" s="3">
-        <v>216400</v>
+        <v>223700</v>
       </c>
       <c r="J23" s="3">
-        <v>160500</v>
+        <v>174000</v>
       </c>
       <c r="K23" s="3">
         <v>172500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>98800</v>
+        <v>98600</v>
       </c>
       <c r="E24" s="3">
-        <v>132700</v>
+        <v>128000</v>
       </c>
       <c r="F24" s="3">
-        <v>68900</v>
+        <v>70700</v>
       </c>
       <c r="G24" s="3">
-        <v>54100</v>
+        <v>59700</v>
       </c>
       <c r="H24" s="3">
-        <v>58200</v>
+        <v>58900</v>
       </c>
       <c r="I24" s="3">
-        <v>53700</v>
+        <v>55500</v>
       </c>
       <c r="J24" s="3">
-        <v>4700</v>
+        <v>5100</v>
       </c>
       <c r="K24" s="3">
         <v>47000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>371200</v>
+        <v>370400</v>
       </c>
       <c r="E26" s="3">
-        <v>629700</v>
+        <v>607600</v>
       </c>
       <c r="F26" s="3">
-        <v>345600</v>
+        <v>354900</v>
       </c>
       <c r="G26" s="3">
-        <v>110700</v>
+        <v>122200</v>
       </c>
       <c r="H26" s="3">
-        <v>291000</v>
+        <v>294900</v>
       </c>
       <c r="I26" s="3">
-        <v>162700</v>
+        <v>168200</v>
       </c>
       <c r="J26" s="3">
-        <v>155800</v>
+        <v>168900</v>
       </c>
       <c r="K26" s="3">
         <v>125500</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>370300</v>
+        <v>369600</v>
       </c>
       <c r="E27" s="3">
-        <v>629000</v>
+        <v>606900</v>
       </c>
       <c r="F27" s="3">
-        <v>344100</v>
+        <v>353400</v>
       </c>
       <c r="G27" s="3">
-        <v>98100</v>
+        <v>108300</v>
       </c>
       <c r="H27" s="3">
-        <v>275900</v>
+        <v>279500</v>
       </c>
       <c r="I27" s="3">
+        <v>152800</v>
+      </c>
+      <c r="J27" s="3">
         <v>147900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>136400</v>
       </c>
       <c r="K27" s="3">
         <v>89200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-22500</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="3">
-        <v>-16400</v>
+        <v>13600</v>
       </c>
       <c r="F32" s="3">
-        <v>-1600</v>
+        <v>-1000</v>
       </c>
       <c r="G32" s="3">
-        <v>3200</v>
+        <v>-6100</v>
       </c>
       <c r="H32" s="3">
-        <v>7500</v>
+        <v>-9700</v>
       </c>
       <c r="I32" s="3">
-        <v>1800</v>
+        <v>-7100</v>
       </c>
       <c r="J32" s="3">
-        <v>-5500</v>
+        <v>1400</v>
       </c>
       <c r="K32" s="3">
         <v>-4300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>370300</v>
+        <v>369600</v>
       </c>
       <c r="E33" s="3">
-        <v>629000</v>
+        <v>606900</v>
       </c>
       <c r="F33" s="3">
-        <v>344100</v>
+        <v>354700</v>
       </c>
       <c r="G33" s="3">
-        <v>98100</v>
+        <v>121900</v>
       </c>
       <c r="H33" s="3">
-        <v>275900</v>
+        <v>294300</v>
       </c>
       <c r="I33" s="3">
-        <v>147900</v>
+        <v>168400</v>
       </c>
       <c r="J33" s="3">
-        <v>136400</v>
+        <v>164800</v>
       </c>
       <c r="K33" s="3">
         <v>89200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>370300</v>
+        <v>369600</v>
       </c>
       <c r="E35" s="3">
-        <v>629000</v>
+        <v>606900</v>
       </c>
       <c r="F35" s="3">
-        <v>344100</v>
+        <v>354700</v>
       </c>
       <c r="G35" s="3">
-        <v>98100</v>
+        <v>121900</v>
       </c>
       <c r="H35" s="3">
-        <v>275900</v>
+        <v>294300</v>
       </c>
       <c r="I35" s="3">
-        <v>147900</v>
+        <v>168400</v>
       </c>
       <c r="J35" s="3">
-        <v>136400</v>
+        <v>164800</v>
       </c>
       <c r="K35" s="3">
         <v>89200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>458700</v>
+        <v>457700</v>
       </c>
       <c r="E41" s="3">
-        <v>332300</v>
+        <v>320600</v>
       </c>
       <c r="F41" s="3">
-        <v>403500</v>
+        <v>414300</v>
       </c>
       <c r="G41" s="3">
-        <v>737800</v>
+        <v>814900</v>
       </c>
       <c r="H41" s="3">
-        <v>142600</v>
+        <v>144500</v>
       </c>
       <c r="I41" s="3">
-        <v>180600</v>
+        <v>186700</v>
       </c>
       <c r="J41" s="3">
-        <v>187500</v>
+        <v>203200</v>
       </c>
       <c r="K41" s="3">
         <v>214400</v>
@@ -2041,22 +2041,22 @@
         <v>6700</v>
       </c>
       <c r="E42" s="3">
-        <v>6200</v>
+        <v>5900</v>
       </c>
       <c r="F42" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="G42" s="3">
-        <v>7200</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="3">
-        <v>7600</v>
+        <v>11100</v>
       </c>
       <c r="I42" s="3">
-        <v>6800</v>
+        <v>18000</v>
       </c>
       <c r="J42" s="3">
-        <v>87500</v>
+        <v>64500</v>
       </c>
       <c r="K42" s="3">
         <v>57400</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>502900</v>
+        <v>484600</v>
       </c>
       <c r="E43" s="3">
-        <v>577700</v>
+        <v>529000</v>
       </c>
       <c r="F43" s="3">
-        <v>556200</v>
+        <v>539300</v>
       </c>
       <c r="G43" s="3">
-        <v>375300</v>
+        <v>402700</v>
       </c>
       <c r="H43" s="3">
-        <v>389500</v>
+        <v>377300</v>
       </c>
       <c r="I43" s="3">
-        <v>376100</v>
+        <v>368300</v>
       </c>
       <c r="J43" s="3">
-        <v>328700</v>
+        <v>387200</v>
       </c>
       <c r="K43" s="3">
         <v>286200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1277900</v>
+        <v>1275300</v>
       </c>
       <c r="E44" s="3">
-        <v>1147700</v>
+        <v>1107400</v>
       </c>
       <c r="F44" s="3">
-        <v>978300</v>
+        <v>1004600</v>
       </c>
       <c r="G44" s="3">
-        <v>807500</v>
+        <v>891800</v>
       </c>
       <c r="H44" s="3">
-        <v>916600</v>
+        <v>928700</v>
       </c>
       <c r="I44" s="3">
-        <v>843600</v>
+        <v>872100</v>
       </c>
       <c r="J44" s="3">
-        <v>821400</v>
+        <v>890500</v>
       </c>
       <c r="K44" s="3">
         <v>781600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>51800</v>
+        <v>76300</v>
       </c>
       <c r="E45" s="3">
-        <v>59400</v>
+        <v>95500</v>
       </c>
       <c r="F45" s="3">
-        <v>5000</v>
+        <v>34500</v>
       </c>
       <c r="G45" s="3">
-        <v>13200</v>
+        <v>20800</v>
       </c>
       <c r="H45" s="3">
         <v>3300</v>
       </c>
       <c r="I45" s="3">
-        <v>10600</v>
+        <v>1500</v>
       </c>
       <c r="J45" s="3">
-        <v>25200</v>
+        <v>26800</v>
       </c>
       <c r="K45" s="3">
         <v>22100</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2298000</v>
+        <v>2321600</v>
       </c>
       <c r="E46" s="3">
-        <v>2123300</v>
+        <v>2073500</v>
       </c>
       <c r="F46" s="3">
-        <v>1950100</v>
+        <v>2015200</v>
       </c>
       <c r="G46" s="3">
-        <v>1941100</v>
+        <v>2150000</v>
       </c>
       <c r="H46" s="3">
-        <v>1459700</v>
+        <v>1482300</v>
       </c>
       <c r="I46" s="3">
-        <v>1417700</v>
+        <v>1467000</v>
       </c>
       <c r="J46" s="3">
-        <v>1450200</v>
+        <v>1572200</v>
       </c>
       <c r="K46" s="3">
         <v>1361700</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>65100</v>
+        <v>55200</v>
       </c>
       <c r="E47" s="3">
-        <v>48500</v>
+        <v>39300</v>
       </c>
       <c r="F47" s="3">
-        <v>44600</v>
+        <v>40400</v>
       </c>
       <c r="G47" s="3">
-        <v>69100</v>
+        <v>45400</v>
       </c>
       <c r="H47" s="3">
-        <v>57700</v>
+        <v>40500</v>
       </c>
       <c r="I47" s="3">
-        <v>58200</v>
+        <v>38900</v>
       </c>
       <c r="J47" s="3">
-        <v>31100</v>
+        <v>22100</v>
       </c>
       <c r="K47" s="3">
         <v>29900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2668900</v>
+        <v>2614500</v>
       </c>
       <c r="E48" s="3">
-        <v>2555000</v>
+        <v>2424800</v>
       </c>
       <c r="F48" s="3">
-        <v>2392500</v>
+        <v>2406600</v>
       </c>
       <c r="G48" s="3">
-        <v>2000000</v>
+        <v>2147400</v>
       </c>
       <c r="H48" s="3">
-        <v>2149300</v>
+        <v>2112700</v>
       </c>
       <c r="I48" s="3">
-        <v>1819000</v>
+        <v>1804100</v>
       </c>
       <c r="J48" s="3">
-        <v>1758300</v>
+        <v>1827100</v>
       </c>
       <c r="K48" s="3">
         <v>1795900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>946900</v>
+        <v>944900</v>
       </c>
       <c r="E49" s="3">
-        <v>937900</v>
+        <v>905000</v>
       </c>
       <c r="F49" s="3">
-        <v>949600</v>
+        <v>975100</v>
       </c>
       <c r="G49" s="3">
-        <v>715000</v>
+        <v>789700</v>
       </c>
       <c r="H49" s="3">
-        <v>842200</v>
+        <v>853300</v>
       </c>
       <c r="I49" s="3">
-        <v>789400</v>
+        <v>816000</v>
       </c>
       <c r="J49" s="3">
-        <v>765200</v>
+        <v>829600</v>
       </c>
       <c r="K49" s="3">
         <v>751300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>78100</v>
+        <v>58700</v>
       </c>
       <c r="E52" s="3">
-        <v>94000</v>
+        <v>48000</v>
       </c>
       <c r="F52" s="3">
-        <v>94700</v>
+        <v>55400</v>
       </c>
       <c r="G52" s="3">
-        <v>67500</v>
+        <v>92300</v>
       </c>
       <c r="H52" s="3">
-        <v>68300</v>
+        <v>82900</v>
       </c>
       <c r="I52" s="3">
-        <v>61400</v>
+        <v>97400</v>
       </c>
       <c r="J52" s="3">
-        <v>48800</v>
+        <v>90800</v>
       </c>
       <c r="K52" s="3">
         <v>18900</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6057000</v>
+        <v>6044600</v>
       </c>
       <c r="E54" s="3">
-        <v>5758700</v>
+        <v>5556500</v>
       </c>
       <c r="F54" s="3">
-        <v>5431400</v>
+        <v>5576900</v>
       </c>
       <c r="G54" s="3">
-        <v>4792600</v>
+        <v>5293000</v>
       </c>
       <c r="H54" s="3">
-        <v>4577300</v>
+        <v>4637600</v>
       </c>
       <c r="I54" s="3">
-        <v>4145600</v>
+        <v>4285400</v>
       </c>
       <c r="J54" s="3">
-        <v>4053700</v>
+        <v>4394600</v>
       </c>
       <c r="K54" s="3">
         <v>3957600</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>365600</v>
+        <v>364800</v>
       </c>
       <c r="E57" s="3">
-        <v>486900</v>
+        <v>469800</v>
       </c>
       <c r="F57" s="3">
-        <v>468600</v>
+        <v>481200</v>
       </c>
       <c r="G57" s="3">
-        <v>332100</v>
+        <v>366800</v>
       </c>
       <c r="H57" s="3">
-        <v>372600</v>
+        <v>377500</v>
       </c>
       <c r="I57" s="3">
-        <v>362100</v>
+        <v>374300</v>
       </c>
       <c r="J57" s="3">
-        <v>356100</v>
+        <v>386100</v>
       </c>
       <c r="K57" s="3">
         <v>329400</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>472500</v>
+        <v>471600</v>
       </c>
       <c r="E58" s="3">
-        <v>229400</v>
+        <v>221400</v>
       </c>
       <c r="F58" s="3">
-        <v>235900</v>
+        <v>242200</v>
       </c>
       <c r="G58" s="3">
-        <v>484800</v>
+        <v>535400</v>
       </c>
       <c r="H58" s="3">
-        <v>509700</v>
+        <v>516500</v>
       </c>
       <c r="I58" s="3">
-        <v>140600</v>
+        <v>145300</v>
       </c>
       <c r="J58" s="3">
-        <v>355200</v>
+        <v>385100</v>
       </c>
       <c r="K58" s="3">
         <v>435200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>522000</v>
+        <v>451600</v>
       </c>
       <c r="E59" s="3">
-        <v>608100</v>
+        <v>515000</v>
       </c>
       <c r="F59" s="3">
-        <v>506000</v>
+        <v>435500</v>
       </c>
       <c r="G59" s="3">
-        <v>419200</v>
+        <v>370000</v>
       </c>
       <c r="H59" s="3">
-        <v>400200</v>
+        <v>332200</v>
       </c>
       <c r="I59" s="3">
-        <v>378300</v>
+        <v>321800</v>
       </c>
       <c r="J59" s="3">
-        <v>336000</v>
+        <v>287900</v>
       </c>
       <c r="K59" s="3">
         <v>301100</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1360100</v>
+        <v>1370000</v>
       </c>
       <c r="E60" s="3">
-        <v>1324400</v>
+        <v>1293600</v>
       </c>
       <c r="F60" s="3">
-        <v>1210500</v>
+        <v>1243000</v>
       </c>
       <c r="G60" s="3">
-        <v>1236100</v>
+        <v>1365200</v>
       </c>
       <c r="H60" s="3">
-        <v>1282500</v>
+        <v>1299500</v>
       </c>
       <c r="I60" s="3">
-        <v>881000</v>
+        <v>910700</v>
       </c>
       <c r="J60" s="3">
-        <v>1047300</v>
+        <v>1135400</v>
       </c>
       <c r="K60" s="3">
         <v>1065600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1411700</v>
+        <v>1408800</v>
       </c>
       <c r="E61" s="3">
-        <v>1379000</v>
+        <v>1330600</v>
       </c>
       <c r="F61" s="3">
-        <v>1468800</v>
+        <v>1508100</v>
       </c>
       <c r="G61" s="3">
-        <v>1284600</v>
+        <v>1418700</v>
       </c>
       <c r="H61" s="3">
-        <v>638300</v>
+        <v>646700</v>
       </c>
       <c r="I61" s="3">
-        <v>787000</v>
+        <v>813600</v>
       </c>
       <c r="J61" s="3">
-        <v>547100</v>
+        <v>593100</v>
       </c>
       <c r="K61" s="3">
         <v>523800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>328800</v>
+        <v>178000</v>
       </c>
       <c r="E62" s="3">
-        <v>324900</v>
+        <v>161400</v>
       </c>
       <c r="F62" s="3">
-        <v>371800</v>
+        <v>189600</v>
       </c>
       <c r="G62" s="3">
-        <v>334700</v>
+        <v>173400</v>
       </c>
       <c r="H62" s="3">
-        <v>356200</v>
+        <v>155700</v>
       </c>
       <c r="I62" s="3">
-        <v>329900</v>
+        <v>149400</v>
       </c>
       <c r="J62" s="3">
-        <v>342400</v>
+        <v>153500</v>
       </c>
       <c r="K62" s="3">
         <v>356300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3115800</v>
+        <v>3107000</v>
       </c>
       <c r="E66" s="3">
-        <v>3046300</v>
+        <v>2937700</v>
       </c>
       <c r="F66" s="3">
-        <v>3052100</v>
+        <v>3132900</v>
       </c>
       <c r="G66" s="3">
-        <v>2856200</v>
+        <v>3153600</v>
       </c>
       <c r="H66" s="3">
-        <v>2277900</v>
+        <v>2307000</v>
       </c>
       <c r="I66" s="3">
-        <v>1998600</v>
+        <v>2065300</v>
       </c>
       <c r="J66" s="3">
-        <v>1962800</v>
+        <v>2099700</v>
       </c>
       <c r="K66" s="3">
         <v>1967300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2128300</v>
+        <v>2124000</v>
       </c>
       <c r="E72" s="3">
-        <v>1858400</v>
+        <v>1793200</v>
       </c>
       <c r="F72" s="3">
-        <v>1317700</v>
+        <v>1353000</v>
       </c>
       <c r="G72" s="3">
-        <v>1048000</v>
+        <v>1157400</v>
       </c>
       <c r="H72" s="3">
-        <v>1045400</v>
+        <v>1059200</v>
       </c>
       <c r="I72" s="3">
-        <v>842200</v>
+        <v>870600</v>
       </c>
       <c r="J72" s="3">
-        <v>746500</v>
+        <v>789400</v>
       </c>
       <c r="K72" s="3">
         <v>638400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2941200</v>
+        <v>2935200</v>
       </c>
       <c r="E76" s="3">
-        <v>2712300</v>
+        <v>2617100</v>
       </c>
       <c r="F76" s="3">
-        <v>2379300</v>
+        <v>2443000</v>
       </c>
       <c r="G76" s="3">
-        <v>1936400</v>
+        <v>2138600</v>
       </c>
       <c r="H76" s="3">
-        <v>2299400</v>
+        <v>2329700</v>
       </c>
       <c r="I76" s="3">
-        <v>2147100</v>
+        <v>2219500</v>
       </c>
       <c r="J76" s="3">
-        <v>2090900</v>
+        <v>2266700</v>
       </c>
       <c r="K76" s="3">
         <v>1990300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>370300</v>
+        <v>369600</v>
       </c>
       <c r="E81" s="3">
-        <v>629000</v>
+        <v>606900</v>
       </c>
       <c r="F81" s="3">
-        <v>344100</v>
+        <v>354700</v>
       </c>
       <c r="G81" s="3">
-        <v>98100</v>
+        <v>121900</v>
       </c>
       <c r="H81" s="3">
-        <v>275900</v>
+        <v>294300</v>
       </c>
       <c r="I81" s="3">
-        <v>147900</v>
+        <v>168400</v>
       </c>
       <c r="J81" s="3">
-        <v>136400</v>
+        <v>164800</v>
       </c>
       <c r="K81" s="3">
         <v>89200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>317600</v>
+        <v>277900</v>
       </c>
       <c r="E83" s="3">
-        <v>306000</v>
+        <v>253000</v>
       </c>
       <c r="F83" s="3">
-        <v>278300</v>
+        <v>249500</v>
       </c>
       <c r="G83" s="3">
-        <v>270600</v>
+        <v>263900</v>
       </c>
       <c r="H83" s="3">
-        <v>264700</v>
+        <v>242300</v>
       </c>
       <c r="I83" s="3">
-        <v>206500</v>
+        <v>191600</v>
       </c>
       <c r="J83" s="3">
-        <v>210000</v>
+        <v>206700</v>
       </c>
       <c r="K83" s="3">
         <v>208200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>454100</v>
+        <v>453100</v>
       </c>
       <c r="E89" s="3">
-        <v>801700</v>
+        <v>773500</v>
       </c>
       <c r="F89" s="3">
-        <v>565500</v>
+        <v>580600</v>
       </c>
       <c r="G89" s="3">
-        <v>559000</v>
+        <v>617300</v>
       </c>
       <c r="H89" s="3">
-        <v>476000</v>
+        <v>482300</v>
       </c>
       <c r="I89" s="3">
-        <v>353800</v>
+        <v>365700</v>
       </c>
       <c r="J89" s="3">
-        <v>301600</v>
+        <v>327000</v>
       </c>
       <c r="K89" s="3">
         <v>363200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300800</v>
+        <v>-300200</v>
       </c>
       <c r="E91" s="3">
-        <v>-390500</v>
+        <v>-376800</v>
       </c>
       <c r="F91" s="3">
-        <v>-309900</v>
+        <v>-318200</v>
       </c>
       <c r="G91" s="3">
-        <v>-222700</v>
+        <v>-246000</v>
       </c>
       <c r="H91" s="3">
-        <v>-283000</v>
+        <v>-286700</v>
       </c>
       <c r="I91" s="3">
-        <v>-239100</v>
+        <v>-247100</v>
       </c>
       <c r="J91" s="3">
-        <v>-180700</v>
+        <v>-195900</v>
       </c>
       <c r="K91" s="3">
         <v>-178000</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-357700</v>
+        <v>-357000</v>
       </c>
       <c r="E94" s="3">
-        <v>-368600</v>
+        <v>-355700</v>
       </c>
       <c r="F94" s="3">
-        <v>-738400</v>
+        <v>-758200</v>
       </c>
       <c r="G94" s="3">
-        <v>-163700</v>
+        <v>-180800</v>
       </c>
       <c r="H94" s="3">
-        <v>-292500</v>
+        <v>-296400</v>
       </c>
       <c r="I94" s="3">
-        <v>-234400</v>
+        <v>-242300</v>
       </c>
       <c r="J94" s="3">
-        <v>-197900</v>
+        <v>-214600</v>
       </c>
       <c r="K94" s="3">
         <v>-142700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-105100</v>
+        <v>104800</v>
       </c>
       <c r="E96" s="3">
-        <v>-92900</v>
+        <v>89600</v>
       </c>
       <c r="F96" s="3">
-        <v>-74600</v>
+        <v>88800</v>
       </c>
       <c r="G96" s="3">
-        <v>-74600</v>
+        <v>97700</v>
       </c>
       <c r="H96" s="3">
-        <v>-63500</v>
+        <v>80300</v>
       </c>
       <c r="I96" s="3">
-        <v>-38600</v>
+        <v>55400</v>
       </c>
       <c r="J96" s="3">
-        <v>-35000</v>
+        <v>73800</v>
       </c>
       <c r="K96" s="3">
         <v>-25500</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>42900</v>
+        <v>42800</v>
       </c>
       <c r="E100" s="3">
-        <v>-497100</v>
+        <v>-479600</v>
       </c>
       <c r="F100" s="3">
-        <v>-163500</v>
+        <v>-167900</v>
       </c>
       <c r="G100" s="3">
-        <v>203000</v>
+        <v>224200</v>
       </c>
       <c r="H100" s="3">
-        <v>-222900</v>
+        <v>-225800</v>
       </c>
       <c r="I100" s="3">
-        <v>-125900</v>
+        <v>-130200</v>
       </c>
       <c r="J100" s="3">
-        <v>-133100</v>
+        <v>-144300</v>
       </c>
       <c r="K100" s="3">
         <v>-173200</v>
@@ -4452,16 +4452,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-9700</v>
+        <v>-9600</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="G101" s="3">
-        <v>-3000</v>
+        <v>-3300</v>
       </c>
       <c r="H101" s="3">
         <v>1400</v>
@@ -4470,7 +4470,7 @@
         <v>-300</v>
       </c>
       <c r="J101" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="K101" s="3">
         <v>-1500</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>129600</v>
+        <v>129400</v>
       </c>
       <c r="E102" s="3">
-        <v>-64100</v>
+        <v>-61800</v>
       </c>
       <c r="F102" s="3">
-        <v>-334300</v>
+        <v>-343300</v>
       </c>
       <c r="G102" s="3">
-        <v>595200</v>
+        <v>657400</v>
       </c>
       <c r="H102" s="3">
-        <v>-38000</v>
+        <v>-38500</v>
       </c>
       <c r="I102" s="3">
-        <v>-6800</v>
+        <v>-7100</v>
       </c>
       <c r="J102" s="3">
-        <v>-30700</v>
+        <v>-33300</v>
       </c>
       <c r="K102" s="3">
         <v>45900</v>

--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>WBRBY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4669300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5318700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4516400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4103500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3889900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3784200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3746000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3235800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3144800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3092200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3132700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2586400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2248300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3004700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2886800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3237600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2879700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2649700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2481800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2457400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2514100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2188400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2145400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2164100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2220300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1823800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1527600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1667300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1782500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2081100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1636800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1453800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1408100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1326700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1232000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1047400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>999300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>928100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>912400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>762600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>720700</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,34 +886,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>21600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13200</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E14" s="3">
         <v>7000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-7400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>128500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-14300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>291300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>57900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E15" s="3">
         <v>248000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>229200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>227900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>241200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>218200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>213500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>227700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>69700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>56600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>59100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>67600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>68100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>58000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4315100</v>
+      </c>
+      <c r="E17" s="3">
         <v>4140600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4561300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4044700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3746600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3500600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3503500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3512900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3028500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2973000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3274100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3056600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2610200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2204300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>356900</v>
+      </c>
+      <c r="E18" s="3">
         <v>528800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>757400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>471700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>356900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>389300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>280600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>233200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>207300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>171700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-181900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>76100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>44000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,82 +1211,86 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>71500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>676900</v>
+      </c>
+      <c r="E21" s="3">
         <v>781800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1000300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>698600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>592100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>597800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>487000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>462300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>421000</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
@@ -1262,150 +1298,162 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>241700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>331500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E22" s="3">
         <v>81200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>50500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>44100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>44000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>43700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>46400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>50600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>66600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>75100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>59800</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E23" s="3">
         <v>469000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>735600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>425600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>182000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>353800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>223700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>174000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>172500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>113200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-234900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-39700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>55700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E24" s="3">
         <v>98600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>128000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>70700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>58900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>55500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>47000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E26" s="3">
         <v>370400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>607600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>354900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>122200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>294900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>168200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>168900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>125500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-250500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-44500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>46300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E27" s="3">
         <v>369600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>606900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>353400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>108300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>279500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>152800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>147900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>89200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-285500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-77200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-71500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E33" s="3">
         <v>369600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>606900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>354700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>121900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>294300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>168400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>164800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>89200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-285500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-77200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E35" s="3">
         <v>369600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>606900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>354700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>121900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>294300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>168400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>164800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>89200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-285500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-77200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E41" s="3">
         <v>457700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>320600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>414300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>814900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>144500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>186700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>203200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>214400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>163900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>169000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>584300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>266000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1167700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>116200</v>
+      </c>
+      <c r="E42" s="3">
         <v>6700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>18000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>64500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>61800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>63700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>107600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>79600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100300</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>549400</v>
+      </c>
+      <c r="E43" s="3">
         <v>484600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>529000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>539300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>402700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>377300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>368300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>387200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>286200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>277000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>285600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>331300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>296800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>203800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1336800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1275300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1107400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1004600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>891800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>928700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>872100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>890500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>781600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>797000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>821800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>783500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>766600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>674800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>76300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>95500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2273300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2321600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2073500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2015200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2150000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1482300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1467000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1572200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1361700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1314100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1355000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1822100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1426800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1570600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E47" s="3">
         <v>55200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>39300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>38900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>24500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>25300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>36800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>37700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>161400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3026000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2614500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2424800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2406600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2147400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2112700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1804100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1827100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1795900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1805500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1861600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2048900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2069000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4133600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1161900</v>
+      </c>
+      <c r="E49" s="3">
         <v>944900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>905000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>975100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>789700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>853300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>816000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>829600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>751300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>742100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>765200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>991600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>968500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1595300</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E52" s="3">
         <v>58700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>92300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>82900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>97400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>90800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>54900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49300</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6645000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6044600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5556500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5576900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5293000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4637600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4285400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4394600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3957600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3905800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4027200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4954200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4545400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4685100</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>432300</v>
+      </c>
+      <c r="E57" s="3">
         <v>364800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>469800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>481200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>366800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>377500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>374300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>386100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>329400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>292300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>301400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>315700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>278000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>442200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>626500</v>
+      </c>
+      <c r="E58" s="3">
         <v>471600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>221400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>242200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>535400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>516500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>145300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>385100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>435200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>253800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>261700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>342200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>63800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>987600</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>555400</v>
+      </c>
+      <c r="E59" s="3">
         <v>451600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>515000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>435500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>370000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>332200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>321800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>287900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>301100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>309600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>319300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>332400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>335000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>231300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1614100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1370000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1293600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1243000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1365200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1299500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>910700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1135400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1065600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>855800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>882400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>990300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>676700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>946200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1575500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1408800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1330600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1508100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1418700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>646700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>813600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>593100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>523800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>537000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>553700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>983600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>942900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>603200</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E62" s="3">
         <v>178000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>161400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>189600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>173400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>155700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>149400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>153500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>356300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>339700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>350200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>328600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>330500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>387900</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3660400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3107000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2937700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3132900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3153600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2307000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2065300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2099700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1967300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1751500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1806000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2304700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1953800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1835600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1971900</v>
+      </c>
+      <c r="E72" s="3">
         <v>2124000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1793200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1353000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1157400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1059200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>870600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>789400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>638400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>578700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1781500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1960100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2183900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2222600</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2957800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2935200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2617100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2443000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2138600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2329700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2219500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2266700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1990300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2154200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2221200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2649600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2591600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2849500</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E81" s="3">
         <v>369600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>606900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>354700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>121900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>294300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>168400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>164800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>89200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-285500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-77200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,37 +3885,38 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E83" s="3">
         <v>277900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>253000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>249500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>263900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>242300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>191600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>206700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>208200</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
@@ -3726,15 +3924,18 @@
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>213700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>215900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>610400</v>
+      </c>
+      <c r="E89" s="3">
         <v>453100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>773500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>580600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>617300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>482300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>365700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>327000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>363200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>228000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>235100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>224600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>252000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>192500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-323400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-376800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-318200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-246000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-286700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-247100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-195900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-178000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-134900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-139000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-125400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-133900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-135200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,38 +4382,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-946100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-357000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-355700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-758200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-180800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-296400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-242300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-214600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-142700</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
@@ -4195,15 +4424,18 @@
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-251800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-99600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E96" s="3">
         <v>104800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>89600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>88800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>97700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>80300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>55400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>73800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-25500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-14600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-15100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-16200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-15200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,38 +4642,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>167800</v>
+      </c>
+      <c r="E100" s="3">
         <v>42800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-479600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-167900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>224200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-225800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-130200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-144300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-173200</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
@@ -4439,44 +4684,47 @@
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-273000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
@@ -4484,58 +4732,64 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="E102" s="3">
         <v>129400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-61800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-343300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>657400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>45900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-234300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-241600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>299300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-272400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>61400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>WBRBY</t>
   </si>
@@ -892,8 +892,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>24600</v>
       </c>
       <c r="E12" s="3">
         <v>21600</v>
@@ -989,7 +989,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>52400</v>
+        <v>24900</v>
       </c>
       <c r="E14" s="3">
         <v>7000</v>
@@ -1037,7 +1037,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>364000</v>
+        <v>287200</v>
       </c>
       <c r="E15" s="3">
         <v>248000</v>
@@ -1102,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4315100</v>
+        <v>4343600</v>
       </c>
       <c r="E17" s="3">
         <v>4140600</v>
@@ -1150,7 +1150,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>356900</v>
+        <v>328400</v>
       </c>
       <c r="E18" s="3">
         <v>528800</v>
@@ -1218,7 +1218,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>43900</v>
+        <v>47700</v>
       </c>
       <c r="E20" s="3">
         <v>-5000</v>
@@ -1266,7 +1266,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>676900</v>
+        <v>567900</v>
       </c>
       <c r="E21" s="3">
         <v>781800</v>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>123100</v>
+        <v>119700</v>
       </c>
       <c r="E22" s="3">
         <v>81200</v>
@@ -1794,7 +1794,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-43900</v>
+        <v>-47700</v>
       </c>
       <c r="E32" s="3">
         <v>5000</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>116200</v>
+        <v>20300</v>
       </c>
       <c r="E42" s="3">
         <v>6700</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>549400</v>
+        <v>591800</v>
       </c>
       <c r="E43" s="3">
         <v>484600</v>
@@ -2270,8 +2270,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>36600</v>
       </c>
       <c r="E45" s="3">
         <v>76300</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>68500</v>
+        <v>54200</v>
       </c>
       <c r="E47" s="3">
         <v>55200</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>57500</v>
+        <v>71800</v>
       </c>
       <c r="E52" s="3">
         <v>58700</v>
@@ -2887,10 +2887,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>555400</v>
+        <v>453100</v>
       </c>
       <c r="E59" s="3">
-        <v>451600</v>
+        <v>453600</v>
       </c>
       <c r="F59" s="3">
         <v>515000</v>
@@ -3031,7 +3031,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>264100</v>
+        <v>200000</v>
       </c>
       <c r="E62" s="3">
         <v>178000</v>
@@ -3892,7 +3892,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>364000</v>
+        <v>313100</v>
       </c>
       <c r="E83" s="3">
         <v>277900</v>

--- a/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WBRBY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>WBRBY</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4672000</v>
+        <v>5361000</v>
       </c>
       <c r="E8" s="3">
+        <v>4672300</v>
+      </c>
+      <c r="F8" s="3">
         <v>4669300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5318700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4516400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4103500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3889900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3784200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3746000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3235800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3144800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3092200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3132700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2586400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2248300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3004700</v>
+        <v>3478900</v>
       </c>
       <c r="E9" s="3">
+        <v>3004500</v>
+      </c>
+      <c r="F9" s="3">
         <v>2886800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3237600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2879700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2649700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2481800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2457400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2514100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2188400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2145400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2164100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2220300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1823800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1527600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1667300</v>
+        <v>1882100</v>
       </c>
       <c r="E10" s="3">
+        <v>1667900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1782500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2081100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1636800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1453800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1408100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1326700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1232000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1047400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>999300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>928100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>912400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>762600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>720700</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,37 +899,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>24600</v>
+        <v>27000</v>
       </c>
       <c r="E12" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F12" s="3">
         <v>21600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13200</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24900</v>
+        <v>15300</v>
       </c>
       <c r="E14" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F14" s="3">
         <v>7000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>128500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>291300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>57900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-36000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>287200</v>
+        <v>348700</v>
       </c>
       <c r="E15" s="3">
+        <v>298200</v>
+      </c>
+      <c r="F15" s="3">
         <v>248000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>229200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>227900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>241200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>218200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>213500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>227700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>69700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>56600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>59100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>68100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>58000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4343600</v>
+        <v>4960700</v>
       </c>
       <c r="E17" s="3">
+        <v>4317200</v>
+      </c>
+      <c r="F17" s="3">
         <v>4140600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4561300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4044700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3746600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3500600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3503500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3512900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3028500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2973000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3274100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3056600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2610200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2204300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>328400</v>
+        <v>400400</v>
       </c>
       <c r="E18" s="3">
+        <v>355100</v>
+      </c>
+      <c r="F18" s="3">
         <v>528800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>757400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>471700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>356900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>389300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>280600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>233200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>207300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>171700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-181900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>76100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>44000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,88 +1244,92 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>47700</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3">
+        <v>48700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>51500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>71500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>567900</v>
+        <v>747900</v>
       </c>
       <c r="E21" s="3">
+        <v>604600</v>
+      </c>
+      <c r="F21" s="3">
         <v>781800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1000300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>698600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>592100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>597800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>487000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>462300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>421000</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
@@ -1301,159 +1337,171 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>241700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>331500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>119700</v>
+        <v>123300</v>
       </c>
       <c r="E22" s="3">
+        <v>119100</v>
+      </c>
+      <c r="F22" s="3">
         <v>81200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>44100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>44000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>43700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>66600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>75100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>67400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>59800</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>156600</v>
+        <v>273600</v>
       </c>
       <c r="E23" s="3">
+        <v>157400</v>
+      </c>
+      <c r="F23" s="3">
         <v>469000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>735600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>425600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>182000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>353800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>223700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>174000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>172500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>113200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-234900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-39700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>55700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>69300</v>
+        <v>76300</v>
       </c>
       <c r="E24" s="3">
+        <v>69400</v>
+      </c>
+      <c r="F24" s="3">
         <v>98600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>128000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>70700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>59700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>58900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>55500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>47000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>87300</v>
+        <v>197300</v>
       </c>
       <c r="E26" s="3">
+        <v>88000</v>
+      </c>
+      <c r="F26" s="3">
         <v>370400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>607600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>354900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>122200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>294900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>168200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>168900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>125500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-250500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>46300</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>82600</v>
+        <v>194900</v>
       </c>
       <c r="E27" s="3">
+        <v>82800</v>
+      </c>
+      <c r="F27" s="3">
         <v>369600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>606900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>353400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>108300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>279500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>152800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>147900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>89200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>38700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-285500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-77200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-47700</v>
+        <v>-1200</v>
       </c>
       <c r="E32" s="3">
+        <v>-48700</v>
+      </c>
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-51500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-71500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>82600</v>
+        <v>194900</v>
       </c>
       <c r="E33" s="3">
+        <v>82800</v>
+      </c>
+      <c r="F33" s="3">
         <v>369600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>606900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>354700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>121900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>294300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>168400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>164800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>89200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>38700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-285500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-77200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>82600</v>
+        <v>194900</v>
       </c>
       <c r="E35" s="3">
+        <v>82800</v>
+      </c>
+      <c r="F35" s="3">
         <v>369600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>606900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>354700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>121900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>294300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>168400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>164800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>89200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>38700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-285500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-77200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>271000</v>
+        <v>250100</v>
       </c>
       <c r="E41" s="3">
+        <v>271200</v>
+      </c>
+      <c r="F41" s="3">
         <v>457700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>320600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>414300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>814900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>144500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>186700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>203200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>214400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>163900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>169000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>584300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>266000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1167700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20300</v>
+        <v>15300</v>
       </c>
       <c r="E42" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F42" s="3">
         <v>6700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>64500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>61800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>63700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>107600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>79600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>100300</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>591800</v>
+        <v>452000</v>
       </c>
       <c r="E43" s="3">
+        <v>581800</v>
+      </c>
+      <c r="F43" s="3">
         <v>484600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>529000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>539300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>402700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>377300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>368300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>387200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>286200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>277000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>285600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>331300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>296800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>203800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1336800</v>
+        <v>1560400</v>
       </c>
       <c r="E44" s="3">
+        <v>1388300</v>
+      </c>
+      <c r="F44" s="3">
         <v>1275300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1107400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1004600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>891800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>928700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>872100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>890500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>781600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>797000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>821800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>783500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>766600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>674800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>36600</v>
+        <v>57500</v>
       </c>
       <c r="E45" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F45" s="3">
         <v>76300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>95500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2273300</v>
+        <v>2362300</v>
       </c>
       <c r="E46" s="3">
+        <v>2325300</v>
+      </c>
+      <c r="F46" s="3">
         <v>2321600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2073500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2015200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2150000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1482300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1467000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1572200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1361700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1314100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1355000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1822100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1426800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1570600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>54200</v>
+        <v>57500</v>
       </c>
       <c r="E47" s="3">
+        <v>48700</v>
+      </c>
+      <c r="F47" s="3">
         <v>55200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>40500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>38900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>36800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>37700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>161400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3026000</v>
+        <v>3407300</v>
       </c>
       <c r="E48" s="3">
+        <v>3026200</v>
+      </c>
+      <c r="F48" s="3">
         <v>2614500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2424800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2406600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2147400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2112700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1804100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1827100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1795900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1805500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1861600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2048900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2069000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4133600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1161900</v>
+        <v>1242200</v>
       </c>
       <c r="E49" s="3">
+        <v>1109800</v>
+      </c>
+      <c r="F49" s="3">
         <v>944900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>905000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>975100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>789700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>853300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>816000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>829600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>751300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>742100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>765200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>991600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>968500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1595300</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>71800</v>
+        <v>76300</v>
       </c>
       <c r="E52" s="3">
+        <v>71400</v>
+      </c>
+      <c r="F52" s="3">
         <v>58700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>92300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>82900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>97400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>90800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>49300</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6645000</v>
+        <v>7211500</v>
       </c>
       <c r="E54" s="3">
+        <v>6644600</v>
+      </c>
+      <c r="F54" s="3">
         <v>6044600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5556500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5576900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5293000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4637600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4285400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4394600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3957600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3905800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4027200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4954200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4545400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4685100</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>432300</v>
+        <v>533100</v>
       </c>
       <c r="E57" s="3">
+        <v>432800</v>
+      </c>
+      <c r="F57" s="3">
         <v>364800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>469800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>481200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>366800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>377500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>374300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>386100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>329400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>292300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>301400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>315700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>278000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>442200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>626500</v>
+        <v>393300</v>
       </c>
       <c r="E58" s="3">
+        <v>625300</v>
+      </c>
+      <c r="F58" s="3">
         <v>471600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>221400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>242200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>535400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>516500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>145300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>385100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>435200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>253800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>261700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>342200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>63800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>987600</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>453100</v>
+        <v>324100</v>
       </c>
       <c r="E59" s="3">
+        <v>288800</v>
+      </c>
+      <c r="F59" s="3">
         <v>453600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>515000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>435500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>370000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>332200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>321800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>287900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>301100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>309600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>319300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>332400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>335000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>231300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1614100</v>
+        <v>1558100</v>
       </c>
       <c r="E60" s="3">
+        <v>1614000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1370000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1293600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1243000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1365200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1299500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>910700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1135400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1065600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>855800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>882400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>990300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>676700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>946200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1575500</v>
+        <v>1857500</v>
       </c>
       <c r="E61" s="3">
+        <v>1574700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1408800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1330600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1508100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1418700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>646700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>813600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>593100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>523800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>537000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>553700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>983600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>942900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>603200</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200000</v>
+        <v>232500</v>
       </c>
       <c r="E62" s="3">
+        <v>192600</v>
+      </c>
+      <c r="F62" s="3">
         <v>178000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>161400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>189600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>173400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>155700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>149400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>153500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>356300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>339700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>350200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>328600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>330500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>387900</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3660400</v>
+        <v>3921600</v>
       </c>
       <c r="E66" s="3">
+        <v>3659800</v>
+      </c>
+      <c r="F66" s="3">
         <v>3107000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2937700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3132900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3153600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2307000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2065300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2099700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1967300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1751500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1806000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2304700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1953800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1835600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1971900</v>
+        <v>2310700</v>
       </c>
       <c r="E72" s="3">
+        <v>1972300</v>
+      </c>
+      <c r="F72" s="3">
         <v>2124000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1793200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1353000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1157400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1059200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>870600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>789400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>638400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>578700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1781500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1960100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2183900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2222600</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2957800</v>
+        <v>3284000</v>
       </c>
       <c r="E76" s="3">
+        <v>2957900</v>
+      </c>
+      <c r="F76" s="3">
         <v>2935200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2617100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2443000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2138600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2329700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2219500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2266700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1990300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2154200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2221200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2649600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2591600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2849500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>82600</v>
+        <v>194900</v>
       </c>
       <c r="E81" s="3">
+        <v>82800</v>
+      </c>
+      <c r="F81" s="3">
         <v>369600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>606900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>354700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>121900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>294300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>168400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>164800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>89200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>38700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-285500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-77200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,40 +4083,41 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>313100</v>
+        <v>379200</v>
       </c>
       <c r="E83" s="3">
+        <v>323000</v>
+      </c>
+      <c r="F83" s="3">
         <v>277900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>253000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>249500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>263900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>242300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>191600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>206700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>208200</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
@@ -3927,15 +4125,18 @@
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>213700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>215900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>610400</v>
+        <v>739700</v>
       </c>
       <c r="E89" s="3">
+        <v>627400</v>
+      </c>
+      <c r="F89" s="3">
         <v>453100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>773500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>580600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>617300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>482300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>365700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>327000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>363200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>228000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>235100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>224600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>252000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>192500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-323400</v>
+        <v>-329900</v>
       </c>
       <c r="E91" s="3">
+        <v>-323000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-376800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-318200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-246000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-286700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-247100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-195900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-178000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-134900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-139000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-125400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-133900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-135200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,41 +4611,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-946100</v>
+        <v>-275900</v>
       </c>
       <c r="E94" s="3">
+        <v>-962800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-357000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-355700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-758200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-180800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-296400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-242300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-214600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-142700</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
@@ -4427,15 +4656,18 @@
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-251800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-99600</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>103800</v>
+        <v>122100</v>
       </c>
       <c r="E96" s="3">
+        <v>103500</v>
+      </c>
+      <c r="F96" s="3">
         <v>104800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>89600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>88800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>97700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>80300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>55400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>73800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-25500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-14600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-15100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-16200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-13800</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,41 +4887,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>167800</v>
+        <v>-515400</v>
       </c>
       <c r="E100" s="3">
+        <v>167700</v>
+      </c>
+      <c r="F100" s="3">
         <v>42800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-479600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-167900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>224200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-225800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-130200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-144300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-173200</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
@@ -4687,47 +4932,50 @@
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-31300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>500</v>
-      </c>
-      <c r="E101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-9600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
@@ -4735,61 +4983,67 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-167400</v>
+        <v>-56400</v>
       </c>
       <c r="E102" s="3">
+        <v>-167700</v>
+      </c>
+      <c r="F102" s="3">
         <v>129400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-61800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-343300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>657400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>45900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-234300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-241600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>299300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-272400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>61400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
